--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game Development\Roblox\Games\Deno-Hunt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A91AA31D-88CB-47F9-9FD5-986A524FF8F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732B13ED-AA87-49A4-A0CE-2C50417B8582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="638" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="368">
   <si>
     <t>Dino Hunt — implementation task tracker</t>
   </si>
@@ -97,34 +97,49 @@
     <t>M</t>
   </si>
   <si>
+    <t>Cut</t>
+  </si>
+  <si>
+    <t>Void — no Rojo/Wally. Decided 2026-09-28.</t>
+  </si>
+  <si>
+    <t>DH-002</t>
+  </si>
+  <si>
+    <t>Pin Fusion and Nevermore in wally.toml</t>
+  </si>
+  <si>
+    <t>Exact versions pinned, not ranges. Fusion major recorded in docs (0.3 changed the API).</t>
+  </si>
+  <si>
+    <t>Void — no Wally. Fusion installed from its GitHub .rbxm instead; Nevermore dropped.</t>
+  </si>
+  <si>
+    <t>DH-003</t>
+  </si>
+  <si>
+    <t>Write default.project.json</t>
+  </si>
+  <si>
+    <t>Maps src/shared, src/server, src/client, src/assets per plan section 3</t>
+  </si>
+  <si>
+    <t>Void — no Rojo.</t>
+  </si>
+  <si>
+    <t>DH-004</t>
+  </si>
+  <si>
+    <t>Selene and StyLua config</t>
+  </si>
+  <si>
+    <t>Both run clean on an empty project</t>
+  </si>
+  <si>
     <t>Not started</t>
   </si>
   <si>
-    <t>DH-002</t>
-  </si>
-  <si>
-    <t>Pin Fusion and Nevermore in wally.toml</t>
-  </si>
-  <si>
-    <t>Exact versions pinned, not ranges. Fusion major recorded in docs (0.3 changed the API).</t>
-  </si>
-  <si>
-    <t>DH-003</t>
-  </si>
-  <si>
-    <t>Write default.project.json</t>
-  </si>
-  <si>
-    <t>Maps src/shared, src/server, src/client, src/assets per plan section 3</t>
-  </si>
-  <si>
-    <t>DH-004</t>
-  </si>
-  <si>
-    <t>Selene and StyLua config</t>
-  </si>
-  <si>
-    <t>Both run clean on an empty project</t>
+    <t>Can still run manually against exported source.</t>
   </si>
   <si>
     <t>DH-005</t>
@@ -139,6 +154,12 @@
     <t>shared/Config, shared/Net, shared/Types, shared/Util, server/Services, client/Controllers, client/UI</t>
   </si>
   <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Built in-place: ReplicatedStorage.Shared{Config,Net,Types,Util}, Server.Services, Client{Controllers,UI}.</t>
+  </si>
+  <si>
     <t>DH-006</t>
   </si>
   <si>
@@ -148,6 +169,9 @@
     <t>init.server.luau builds the bag and starts services; init.client.luau mirrors it</t>
   </si>
   <si>
+    <t>ServiceBag + Bootstrap live. Server log: '0 service(s)', no errors.</t>
+  </si>
+  <si>
     <t>DH-007</t>
   </si>
   <si>
@@ -157,6 +181,9 @@
     <t>Edit a file, Rojo syncs, change visible in Dino Hunt place</t>
   </si>
   <si>
+    <t>Void — no Rojo. MCP set_script_source is the authoring path.</t>
+  </si>
+  <si>
     <t>DH-008</t>
   </si>
   <si>
@@ -169,6 +196,9 @@
     <t>One trivial HUD element renders in-game from a file edit. Sets the pattern for every later component.</t>
   </si>
   <si>
+    <t>Client.Bootstrap renders the HUD; Computed followed Value 0-&gt;1. Fusion 0.3 confirmed.</t>
+  </si>
+  <si>
     <t>DH-009</t>
   </si>
   <si>
@@ -925,7 +955,31 @@
     <t>Reserved. Do not plan work into it.</t>
   </si>
   <si>
-    <t>72 tasks</t>
+    <t>DH-073</t>
+  </si>
+  <si>
+    <t>Export the script tree to the repo</t>
+  </si>
+  <si>
+    <t>export_rbxm of the code tree committed to git — the only version control the code has</t>
+  </si>
+  <si>
+    <t>Added 2026-09-28: no Rojo means no automatic git coverage.</t>
+  </si>
+  <si>
+    <t>DH-074</t>
+  </si>
+  <si>
+    <t>Write Maid/Signal/ServiceBag unit checks</t>
+  </si>
+  <si>
+    <t>Each exercised in a playtest: cleanup runs, signal fires, two-phase init order holds</t>
+  </si>
+  <si>
+    <t>Added 2026-09-28: hand-written replacements for Nevermore need proving.</t>
+  </si>
+  <si>
+    <t>74 tasks</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -946,9 +1000,6 @@
     <t>Tasks</t>
   </si>
   <si>
-    <t>Done</t>
-  </si>
-  <si>
     <t>Done (d)</t>
   </si>
   <si>
@@ -1049,9 +1100,6 @@
   </si>
   <si>
     <t>Acceptance criteria met in a Studio play test, verified solo and with 2+ players, no new console errors.</t>
-  </si>
-  <si>
-    <t>Cut</t>
   </si>
   <si>
     <t>Deliberately dropped. Say why in Notes.</t>
@@ -1696,7 +1744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K78"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1712,7 +1760,7 @@
     <col min="11" max="11" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1762,7 +1810,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>14</v>
       </c>
@@ -1789,11 +1837,13 @@
         <v>19</v>
       </c>
       <c r="J6" s="9"/>
-      <c r="K6" s="8"/>
-    </row>
-    <row r="7" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K6" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="6">
         <v>0</v>
@@ -1802,10 +1852,10 @@
         <v>15</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>14</v>
@@ -1820,11 +1870,13 @@
         <v>19</v>
       </c>
       <c r="J7" s="9"/>
-      <c r="K7" s="8"/>
-    </row>
-    <row r="8" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>0</v>
@@ -1833,10 +1885,10 @@
         <v>15</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>14</v>
@@ -1851,11 +1903,13 @@
         <v>19</v>
       </c>
       <c r="J8" s="9"/>
-      <c r="K8" s="8"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K8" s="8" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B9" s="6">
         <v>0</v>
@@ -1864,10 +1918,10 @@
         <v>15</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>14</v>
@@ -1879,29 +1933,31 @@
         <v>18</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J9" s="9"/>
-      <c r="K9" s="8"/>
-    </row>
-    <row r="10" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K9" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6">
         <v>0</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G10" s="10">
         <v>0.25</v>
@@ -1910,29 +1966,31 @@
         <v>18</v>
       </c>
       <c r="I10" s="9" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J10" s="9"/>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K10" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B11" s="6">
         <v>0</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>34</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F11" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="G11" s="10">
         <v>0.5</v>
@@ -1941,14 +1999,16 @@
         <v>18</v>
       </c>
       <c r="I11" s="9" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J11" s="9"/>
-      <c r="K11" s="8"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K11" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="B12" s="6">
         <v>0</v>
@@ -1957,13 +2017,13 @@
         <v>15</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G12" s="10">
         <v>0.25</v>
@@ -1975,26 +2035,28 @@
         <v>19</v>
       </c>
       <c r="J12" s="9"/>
-      <c r="K12" s="8"/>
-    </row>
-    <row r="13" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="K12" s="8" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="B13" s="6">
         <v>0</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="G13" s="10">
         <v>0.5</v>
@@ -2003,29 +2065,31 @@
         <v>18</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="J13" s="9"/>
-      <c r="K13" s="8"/>
+      <c r="K13" s="8" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B14" s="6">
         <v>0</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G14" s="10">
         <v>0.25</v>
@@ -2034,29 +2098,29 @@
         <v>18</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J14" s="9"/>
       <c r="K14" s="8"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B15" s="13">
         <v>1</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G15" s="10">
         <v>0.5</v>
@@ -2065,31 +2129,31 @@
         <v>18</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K15" s="8"/>
     </row>
-    <row r="16" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B16" s="13">
         <v>1</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G16" s="10">
         <v>0.5</v>
@@ -2098,29 +2162,29 @@
         <v>18</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="8"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="B17" s="13">
         <v>1</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="E17" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F17" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>47</v>
       </c>
       <c r="G17" s="10">
         <v>0.5</v>
@@ -2129,31 +2193,31 @@
         <v>18</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K17" s="8"/>
     </row>
-    <row r="18" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="B18" s="13">
         <v>1</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="G18" s="10">
         <v>0.25</v>
@@ -2162,29 +2226,29 @@
         <v>18</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="8"/>
     </row>
-    <row r="19" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B19" s="13">
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G19" s="10">
         <v>0.5</v>
@@ -2193,31 +2257,31 @@
         <v>18</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B20" s="13">
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="G20" s="10">
         <v>0.5</v>
@@ -2226,31 +2290,31 @@
         <v>18</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K20" s="8"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B21" s="13">
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F21" s="9" t="s">
         <v>72</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>62</v>
       </c>
       <c r="G21" s="10">
         <v>0.75</v>
@@ -2259,31 +2323,31 @@
         <v>18</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B22" s="13">
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="G22" s="10">
         <v>0.25</v>
@@ -2292,31 +2356,31 @@
         <v>18</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K22" s="8"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="B23" s="13">
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="E23" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F23" s="9" t="s">
         <v>81</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>71</v>
       </c>
       <c r="G23" s="10">
         <v>0.75</v>
@@ -2325,29 +2389,29 @@
         <v>18</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J23" s="9"/>
       <c r="K23" s="8"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B24" s="13">
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G24" s="10">
         <v>1</v>
@@ -2356,31 +2420,31 @@
         <v>18</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="K24" s="8"/>
     </row>
-    <row r="25" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="B25" s="13">
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="G25" s="10">
         <v>0.5</v>
@@ -2389,31 +2453,31 @@
         <v>18</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="B26" s="15">
         <v>2</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G26" s="10">
         <v>1</v>
@@ -2422,31 +2486,31 @@
         <v>18</v>
       </c>
       <c r="I26" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B27" s="15">
         <v>2</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G27" s="10">
         <v>0.5</v>
@@ -2455,29 +2519,29 @@
         <v>18</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J27" s="9"/>
       <c r="K27" s="8"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B28" s="15">
         <v>2</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="G28" s="10">
         <v>0.5</v>
@@ -2486,31 +2550,31 @@
         <v>18</v>
       </c>
       <c r="I28" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="B29" s="15">
         <v>2</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G29" s="10">
         <v>0.5</v>
@@ -2519,31 +2583,31 @@
         <v>18</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="B30" s="15">
         <v>2</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G30" s="10">
         <v>0.4</v>
@@ -2552,31 +2616,31 @@
         <v>18</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="B31" s="15">
         <v>2</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G31" s="10">
         <v>0.4</v>
@@ -2585,31 +2649,31 @@
         <v>18</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K31" s="8"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="B32" s="15">
         <v>2</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="G32" s="10">
         <v>0.6</v>
@@ -2618,31 +2682,31 @@
         <v>18</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K32" s="8"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="B33" s="15">
         <v>2</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="G33" s="10">
         <v>0.75</v>
@@ -2651,29 +2715,29 @@
         <v>18</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J33" s="9"/>
       <c r="K33" s="8"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B34" s="15">
         <v>2</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G34" s="10">
         <v>0.4</v>
@@ -2682,31 +2746,31 @@
         <v>18</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="B35" s="15">
         <v>2</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G35" s="10">
         <v>0.25</v>
@@ -2715,31 +2779,31 @@
         <v>18</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B36" s="17">
         <v>3</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="G36" s="10">
         <v>0.5</v>
@@ -2748,31 +2812,31 @@
         <v>18</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="K36" s="8"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B37" s="17">
         <v>3</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G37" s="10">
         <v>0.75</v>
@@ -2781,31 +2845,31 @@
         <v>18</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="B38" s="17">
         <v>3</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="G38" s="10">
         <v>0.5</v>
@@ -2814,31 +2878,31 @@
         <v>18</v>
       </c>
       <c r="I38" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="B39" s="17">
         <v>3</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E39" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="F39" s="9" t="s">
         <v>140</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>130</v>
       </c>
       <c r="G39" s="10">
         <v>0.4</v>
@@ -2847,31 +2911,31 @@
         <v>18</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="B40" s="17">
         <v>3</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G40" s="10">
         <v>0.5</v>
@@ -2880,31 +2944,31 @@
         <v>18</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="K40" s="8"/>
     </row>
-    <row r="41" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="B41" s="17">
         <v>3</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G41" s="10">
         <v>0.75</v>
@@ -2913,31 +2977,31 @@
         <v>18</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K41" s="8"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="B42" s="17">
         <v>3</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="G42" s="10">
         <v>0.5</v>
@@ -2946,31 +3010,31 @@
         <v>18</v>
       </c>
       <c r="I42" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="K42" s="8"/>
     </row>
-    <row r="43" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B43" s="17">
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G43" s="10">
         <v>0.5</v>
@@ -2979,31 +3043,31 @@
         <v>18</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="K43" s="8"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="B44" s="17">
         <v>3</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="G44" s="10">
         <v>0.4</v>
@@ -3012,29 +3076,29 @@
         <v>18</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="8"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B45" s="17">
         <v>3</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G45" s="10">
         <v>0.5</v>
@@ -3043,29 +3107,29 @@
         <v>18</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="8"/>
     </row>
-    <row r="46" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B46" s="17">
         <v>3</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G46" s="10">
         <v>0.4</v>
@@ -3074,29 +3138,29 @@
         <v>18</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J46" s="9"/>
       <c r="K46" s="8"/>
     </row>
-    <row r="47" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="B47" s="19">
         <v>4</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G47" s="10">
         <v>1</v>
@@ -3105,31 +3169,31 @@
         <v>18</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="B48" s="19">
         <v>4</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G48" s="10">
         <v>0.75</v>
@@ -3138,31 +3202,31 @@
         <v>18</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="K48" s="8"/>
     </row>
-    <row r="49" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B49" s="19">
         <v>4</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="9" t="s">
         <v>177</v>
-      </c>
-      <c r="E49" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="F49" s="9" t="s">
-        <v>167</v>
       </c>
       <c r="G49" s="10">
         <v>0.25</v>
@@ -3171,31 +3235,31 @@
         <v>18</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="B50" s="19">
         <v>4</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="G50" s="10">
         <v>0.4</v>
@@ -3204,29 +3268,29 @@
         <v>18</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J50" s="9"/>
       <c r="K50" s="8"/>
     </row>
-    <row r="51" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B51" s="19">
         <v>4</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="G51" s="10">
         <v>1.25</v>
@@ -3235,31 +3299,31 @@
         <v>18</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K51" s="8"/>
     </row>
-    <row r="52" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="B52" s="19">
         <v>4</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G52" s="10">
         <v>0.5</v>
@@ -3268,31 +3332,31 @@
         <v>18</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="B53" s="19">
         <v>4</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="G53" s="10">
         <v>0.5</v>
@@ -3301,31 +3365,31 @@
         <v>18</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="B54" s="19">
         <v>4</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D54" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="F54" s="9" t="s">
         <v>197</v>
-      </c>
-      <c r="E54" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F54" s="9" t="s">
-        <v>187</v>
       </c>
       <c r="G54" s="10">
         <v>0.4</v>
@@ -3334,31 +3398,31 @@
         <v>18</v>
       </c>
       <c r="I54" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B55" s="19">
         <v>4</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D55" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="F55" s="9" t="s">
         <v>201</v>
-      </c>
-      <c r="E55" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F55" s="9" t="s">
-        <v>191</v>
       </c>
       <c r="G55" s="10">
         <v>0.5</v>
@@ -3367,31 +3431,31 @@
         <v>18</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="B56" s="19">
         <v>4</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G56" s="10">
         <v>0.5</v>
@@ -3400,31 +3464,31 @@
         <v>18</v>
       </c>
       <c r="I56" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K56" s="8"/>
     </row>
-    <row r="57" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B57" s="19">
         <v>4</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G57" s="10">
         <v>0.5</v>
@@ -3433,31 +3497,31 @@
         <v>18</v>
       </c>
       <c r="I57" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="K57" s="8"/>
     </row>
-    <row r="58" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="B58" s="21">
         <v>5</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G58" s="10">
         <v>1</v>
@@ -3466,31 +3530,31 @@
         <v>18</v>
       </c>
       <c r="I58" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="K58" s="8"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B59" s="21">
         <v>5</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F59" s="9" t="s">
         <v>217</v>
-      </c>
-      <c r="E59" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F59" s="9" t="s">
-        <v>207</v>
       </c>
       <c r="G59" s="10">
         <v>0.4</v>
@@ -3499,31 +3563,31 @@
         <v>18</v>
       </c>
       <c r="I59" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="K59" s="8"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B60" s="21">
         <v>5</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="G60" s="10">
         <v>0.4</v>
@@ -3532,31 +3596,31 @@
         <v>18</v>
       </c>
       <c r="I60" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="K60" s="8"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B61" s="21">
         <v>5</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G61" s="10">
         <v>0.75</v>
@@ -3565,31 +3629,31 @@
         <v>18</v>
       </c>
       <c r="I61" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="K61" s="8"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B62" s="21">
         <v>5</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="E62" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>230</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>220</v>
       </c>
       <c r="G62" s="10">
         <v>0.5</v>
@@ -3598,31 +3662,31 @@
         <v>18</v>
       </c>
       <c r="I62" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B63" s="21">
         <v>5</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D63" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F63" s="9" t="s">
         <v>233</v>
-      </c>
-      <c r="E63" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>223</v>
       </c>
       <c r="G63" s="10">
         <v>0.5</v>
@@ -3631,31 +3695,31 @@
         <v>18</v>
       </c>
       <c r="I63" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K63" s="8"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B64" s="21">
         <v>5</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="E64" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="F64" s="9" t="s">
         <v>238</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="G64" s="10">
         <v>0.75</v>
@@ -3664,31 +3728,31 @@
         <v>18</v>
       </c>
       <c r="I64" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="K64" s="8"/>
     </row>
-    <row r="65" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="B65" s="21">
         <v>5</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="E65" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="F65" s="9" t="s">
         <v>242</v>
-      </c>
-      <c r="F65" s="9" t="s">
-        <v>232</v>
       </c>
       <c r="G65" s="10">
         <v>0.75</v>
@@ -3697,64 +3761,64 @@
         <v>18</v>
       </c>
       <c r="I65" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="K65" s="8"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B66" s="21">
         <v>5</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D66" s="7" t="s">
+        <v>256</v>
+      </c>
+      <c r="E66" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="F66" s="9" t="s">
         <v>246</v>
-      </c>
-      <c r="E66" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="F66" s="9" t="s">
-        <v>236</v>
       </c>
       <c r="G66" s="10">
         <v>0.75</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I66" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="K66" s="8"/>
     </row>
-    <row r="67" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B67" s="21">
         <v>5</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="G67" s="10">
         <v>0.5</v>
@@ -3763,31 +3827,31 @@
         <v>18</v>
       </c>
       <c r="I67" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="K67" s="8"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B68" s="23">
         <v>6</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G68" s="10">
         <v>0.75</v>
@@ -3796,31 +3860,31 @@
         <v>18</v>
       </c>
       <c r="I68" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="K68" s="8"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B69" s="23">
         <v>6</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="G69" s="10">
         <v>0.75</v>
@@ -3829,31 +3893,31 @@
         <v>18</v>
       </c>
       <c r="I69" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="K69" s="8"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B70" s="23">
         <v>6</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="G70" s="10">
         <v>0.4</v>
@@ -3862,31 +3926,31 @@
         <v>18</v>
       </c>
       <c r="I70" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="K70" s="8"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B71" s="23">
         <v>6</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G71" s="10">
         <v>0.4</v>
@@ -3895,31 +3959,31 @@
         <v>18</v>
       </c>
       <c r="I71" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="K71" s="8"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B72" s="23">
         <v>6</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="G72" s="10">
         <v>0.4</v>
@@ -3928,64 +3992,64 @@
         <v>18</v>
       </c>
       <c r="I72" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="B73" s="23">
         <v>6</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="G73" s="10">
         <v>0.6</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="I73" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="K73" s="8"/>
     </row>
-    <row r="74" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B74" s="23">
         <v>6</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G74" s="10">
         <v>0.75</v>
@@ -3994,31 +4058,31 @@
         <v>18</v>
       </c>
       <c r="I74" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="K74" s="8"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B75" s="23">
         <v>6</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D75" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E75" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="F75" s="9" t="s">
         <v>285</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>286</v>
-      </c>
-      <c r="F75" s="9" t="s">
-        <v>275</v>
       </c>
       <c r="G75" s="10">
         <v>0.5</v>
@@ -4027,31 +4091,31 @@
         <v>18</v>
       </c>
       <c r="I75" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="K75" s="8"/>
     </row>
-    <row r="76" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B76" s="23">
         <v>6</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="G76" s="10">
         <v>0.75</v>
@@ -4060,31 +4124,31 @@
         <v>18</v>
       </c>
       <c r="I76" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="K76" s="8"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B77" s="23">
         <v>6</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="E77" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F77" s="9" t="s">
         <v>294</v>
-      </c>
-      <c r="F77" s="9" t="s">
-        <v>284</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -4093,21 +4157,85 @@
         <v>18</v>
       </c>
       <c r="I77" s="9" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J77" s="9"/>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D78" s="24" t="s">
-        <v>295</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="G78" s="25">
-        <f>SUM(G6:G77)</f>
-        <v>39.149999999999991</v>
+    <row r="78" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A78" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="B78" s="23">
+        <v>0</v>
+      </c>
+      <c r="C78" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="F78" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="G78" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="H78" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J78" s="9" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A79" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="B79" s="23">
+        <v>0</v>
+      </c>
+      <c r="C79" s="22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D79" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E79" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="F79" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G79" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H79" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="I79" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J79" s="9" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="D80" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="F80" s="24" t="s">
+        <v>314</v>
+      </c>
+      <c r="G80" s="25">
+        <f>SUM(G6:G79)</f>
+        <v>39.899999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -4153,14 +4281,14 @@
     <col min="9" max="9" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4168,31 +4296,31 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>303</v>
+        <v>320</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>0</v>
       </c>
@@ -4200,30 +4328,30 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>306</v>
+        <v>323</v>
       </c>
       <c r="D5" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A5)</f>
-        <v>9</v>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A5)</f>
+        <v>11</v>
       </c>
       <c r="E5" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A5,Tasks!$I$6:$I$77,"Done")</f>
-        <v>0</v>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
+        <v>3</v>
       </c>
       <c r="F5" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A5)</f>
-        <v>3</v>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5)</f>
+        <v>3.75</v>
       </c>
       <c r="G5" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A5,Tasks!$I$6:$I$77,"Done")</f>
-        <v>0</v>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
+        <v>1.25</v>
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:H12" si="0">IFERROR(G5/F5,0)</f>
-        <v>0</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4231,25 +4359,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>309</v>
+        <v>326</v>
       </c>
       <c r="D6" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A6)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A6)</f>
         <v>11</v>
       </c>
       <c r="E6" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A6,Tasks!$I$6:$I$77,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="F6" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A6)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6)</f>
         <v>6</v>
       </c>
       <c r="G6" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A6,Tasks!$I$6:$I$77,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="H6" s="28">
@@ -4257,7 +4385,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>310</v>
+        <v>327</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4265,25 +4393,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>311</v>
+        <v>328</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>312</v>
+        <v>329</v>
       </c>
       <c r="D7" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A7)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A7)</f>
         <v>10</v>
       </c>
       <c r="E7" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A7,Tasks!$I$6:$I$77,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A7,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="F7" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A7)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A7)</f>
         <v>5.3000000000000007</v>
       </c>
       <c r="G7" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A7,Tasks!$I$6:$I$77,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A7,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="H7" s="28">
@@ -4291,7 +4419,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>313</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4299,25 +4427,25 @@
         <v>3</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>314</v>
+        <v>331</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>315</v>
+        <v>332</v>
       </c>
       <c r="D8" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A8)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A8)</f>
         <v>11</v>
       </c>
       <c r="E8" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A8,Tasks!$I$6:$I$77,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A8,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="F8" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A8)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A8)</f>
         <v>5.7000000000000011</v>
       </c>
       <c r="G8" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A8,Tasks!$I$6:$I$77,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A8,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="H8" s="28">
@@ -4325,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>316</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4333,25 +4461,25 @@
         <v>4</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="D9" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A9)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A9)</f>
         <v>11</v>
       </c>
       <c r="E9" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A9,Tasks!$I$6:$I$77,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A9,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A9)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A9)</f>
         <v>6.5500000000000007</v>
       </c>
       <c r="G9" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A9,Tasks!$I$6:$I$77,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A9,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="H9" s="28">
@@ -4359,33 +4487,33 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="21">
         <v>5</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="D10" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A10)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A10)</f>
         <v>10</v>
       </c>
       <c r="E10" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A10,Tasks!$I$6:$I$77,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A10,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="F10" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A10)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A10)</f>
         <v>6.3</v>
       </c>
       <c r="G10" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A10,Tasks!$I$6:$I$77,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A10,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="H10" s="28">
@@ -4393,7 +4521,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4401,25 +4529,25 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="D11" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A11)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A11)</f>
         <v>10</v>
       </c>
       <c r="E11" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$77,$A11,Tasks!$I$6:$I$77,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$79,$A11,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="F11" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A11)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A11)</f>
         <v>6.3</v>
       </c>
       <c r="G11" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$77,Tasks!$B$6:$B$77,$A11,Tasks!$I$6:$I$77,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A11,Tasks!$I$6:$I$79,"Done")</f>
         <v>0</v>
       </c>
       <c r="H11" s="28">
@@ -4427,40 +4555,40 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="36">
         <f>SUM(D5:D11)</f>
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E12" s="36">
         <f>SUM(E5:E11)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F12" s="37">
         <f>SUM(F5:F11)</f>
-        <v>39.15</v>
+        <v>39.9</v>
       </c>
       <c r="G12" s="37">
         <f>SUM(G5:G11)</f>
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="H12" s="38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.1328320802005011E-2</v>
       </c>
       <c r="I12" s="35"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="39" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>
@@ -4477,21 +4605,21 @@
     <col min="2" max="2" width="108" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="24"/>
       <c r="B3" s="40"/>
     </row>
-    <row r="4" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4500,48 +4628,48 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="B6" s="40"/>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="24" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="24" t="s">
-        <v>302</v>
+        <v>38</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>337</v>
+        <v>19</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>338</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4550,7 +4678,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>339</v>
+        <v>355</v>
       </c>
       <c r="B13" s="40"/>
     </row>
@@ -4559,23 +4687,23 @@
         <v>18</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>340</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>341</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>342</v>
+        <v>358</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>343</v>
+        <v>359</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4584,7 +4712,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>344</v>
+        <v>360</v>
       </c>
       <c r="B18" s="40"/>
     </row>
@@ -4593,7 +4721,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>345</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4601,39 +4729,39 @@
         <v>9</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="24" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="24"/>
       <c r="B22" s="40"/>
     </row>
-    <row r="23" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>349</v>
+        <v>365</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="24"/>
       <c r="B24" s="40"/>
     </row>
-    <row r="25" spans="1:2" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>350</v>
+        <v>366</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>351</v>
+        <v>367</v>
       </c>
     </row>
   </sheetData>

--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game Development\Roblox\Games\Deno-Hunt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732B13ED-AA87-49A4-A0CE-2C50417B8582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB6769E-54FD-451B-9248-416078197A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="373">
   <si>
     <t>Dino Hunt — implementation task tracker</t>
   </si>
@@ -226,6 +226,9 @@
     <t>FR-10</t>
   </si>
   <si>
+    <t>Plaza 180x180, reactor at origin, 60-stud defense ring. Ring needed a fix: a Cylinder's X axis is its length, so (60,0.2,60) stood a pillar up instead of laying a disc.</t>
+  </si>
+  <si>
     <t>DH-011</t>
   </si>
   <si>
@@ -235,6 +238,9 @@
     <t>2-3 lanes that read clearly from the reactor; spawn points marked</t>
   </si>
   <si>
+    <t>3 lanes N/E/W, 28 wide x 130 long, 14-high walls, spawn markers. OpensAtWave attribute set: 1 / 6 / 11.</t>
+  </si>
+  <si>
     <t>DH-012</t>
   </si>
   <si>
@@ -247,6 +253,9 @@
     <t>FR-30</t>
   </si>
   <si>
+    <t>4 sector pads on the diagonals behind colour-coded gates, plus 6 containment bays on the south edge. Corridor yaws derived from each diagonal, not hardcoded.</t>
+  </si>
+  <si>
     <t>DH-013</t>
   </si>
   <si>
@@ -256,6 +265,9 @@
     <t>Committed under src/assets; replaceable without touching code</t>
   </si>
   <si>
+    <t>snapshot/DinoHunt-Snapshot.rbxm, 21KB, covering Map + Shared + Server + Client.</t>
+  </si>
+  <si>
     <t>DH-014</t>
   </si>
   <si>
@@ -965,6 +977,9 @@
   </si>
   <si>
     <t>Added 2026-09-28: no Rojo means no automatic git coverage.</t>
+  </si>
+  <si>
+    <t>Snapshot committed with a README covering restore steps and the binary-diff limitation.</t>
   </si>
   <si>
     <t>DH-074</t>
@@ -1907,7 +1922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>29</v>
       </c>
@@ -2006,7 +2021,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>44</v>
       </c>
@@ -2103,7 +2118,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>57</v>
       </c>
@@ -2129,16 +2144,18 @@
         <v>18</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K15" s="8"/>
+      <c r="K15" s="8" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B16" s="13">
         <v>1</v>
@@ -2147,10 +2164,10 @@
         <v>58</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>57</v>
@@ -2162,14 +2179,16 @@
         <v>18</v>
       </c>
       <c r="I16" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J16" s="9"/>
-      <c r="K16" s="8"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K16" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B17" s="13">
         <v>1</v>
@@ -2178,10 +2197,10 @@
         <v>58</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>57</v>
@@ -2193,16 +2212,18 @@
         <v>18</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="8"/>
+        <v>70</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="18" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B18" s="13">
         <v>1</v>
@@ -2211,13 +2232,13 @@
         <v>58</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G18" s="10">
         <v>0.25</v>
@@ -2226,26 +2247,28 @@
         <v>18</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J18" s="9"/>
-      <c r="K18" s="8"/>
+      <c r="K18" s="8" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="19" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B19" s="13">
         <v>1</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>53</v>
@@ -2260,25 +2283,25 @@
         <v>32</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K19" s="8"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B20" s="13">
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>53</v>
@@ -2293,28 +2316,28 @@
         <v>32</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K20" s="8"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B21" s="13">
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G21" s="10">
         <v>0.75</v>
@@ -2326,28 +2349,28 @@
         <v>32</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="K21" s="8"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B22" s="13">
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G22" s="10">
         <v>0.25</v>
@@ -2359,28 +2382,28 @@
         <v>32</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K22" s="8"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B23" s="13">
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="G23" s="10">
         <v>0.75</v>
@@ -2396,19 +2419,19 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B24" s="13">
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>40</v>
@@ -2423,28 +2446,28 @@
         <v>32</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K24" s="8"/>
     </row>
     <row r="25" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B25" s="13">
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="G25" s="10">
         <v>0.5</v>
@@ -2456,28 +2479,28 @@
         <v>32</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K25" s="8"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B26" s="15">
         <v>2</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G26" s="10">
         <v>1</v>
@@ -2489,28 +2512,28 @@
         <v>32</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B27" s="15">
         <v>2</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G27" s="10">
         <v>0.5</v>
@@ -2526,22 +2549,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B28" s="15">
         <v>2</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D28" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F28" s="9" t="s">
         <v>110</v>
-      </c>
-      <c r="E28" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="G28" s="10">
         <v>0.5</v>
@@ -2553,28 +2576,28 @@
         <v>32</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B29" s="15">
         <v>2</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G29" s="10">
         <v>0.5</v>
@@ -2586,28 +2609,28 @@
         <v>32</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B30" s="15">
         <v>2</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G30" s="10">
         <v>0.4</v>
@@ -2619,28 +2642,28 @@
         <v>32</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K30" s="8"/>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B31" s="15">
         <v>2</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G31" s="10">
         <v>0.4</v>
@@ -2652,28 +2675,28 @@
         <v>32</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K31" s="8"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B32" s="15">
         <v>2</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="G32" s="10">
         <v>0.6</v>
@@ -2685,28 +2708,28 @@
         <v>32</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="K32" s="8"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B33" s="15">
         <v>2</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G33" s="10">
         <v>0.75</v>
@@ -2722,22 +2745,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B34" s="15">
         <v>2</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G34" s="10">
         <v>0.4</v>
@@ -2749,28 +2772,28 @@
         <v>32</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B35" s="15">
         <v>2</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G35" s="10">
         <v>0.25</v>
@@ -2782,25 +2805,25 @@
         <v>32</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B36" s="17">
         <v>3</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>57</v>
@@ -2821,22 +2844,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B37" s="17">
         <v>3</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G37" s="10">
         <v>0.75</v>
@@ -2848,28 +2871,28 @@
         <v>32</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B38" s="17">
         <v>3</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G38" s="10">
         <v>0.5</v>
@@ -2881,28 +2904,28 @@
         <v>32</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B39" s="17">
         <v>3</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G39" s="10">
         <v>0.4</v>
@@ -2914,28 +2937,28 @@
         <v>32</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B40" s="17">
         <v>3</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G40" s="10">
         <v>0.5</v>
@@ -2947,28 +2970,28 @@
         <v>32</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="K40" s="8"/>
     </row>
     <row r="41" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B41" s="17">
         <v>3</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="G41" s="10">
         <v>0.75</v>
@@ -2980,28 +3003,28 @@
         <v>32</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="K41" s="8"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B42" s="17">
         <v>3</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="G42" s="10">
         <v>0.5</v>
@@ -3013,28 +3036,28 @@
         <v>32</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B43" s="17">
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G43" s="10">
         <v>0.5</v>
@@ -3046,13 +3069,13 @@
         <v>32</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="K43" s="8"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B44" s="17">
         <v>3</v>
@@ -3061,13 +3084,13 @@
         <v>49</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="G44" s="10">
         <v>0.4</v>
@@ -3083,7 +3106,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B45" s="17">
         <v>3</v>
@@ -3092,13 +3115,13 @@
         <v>49</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="G45" s="10">
         <v>0.5</v>
@@ -3114,7 +3137,7 @@
     </row>
     <row r="46" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B46" s="17">
         <v>3</v>
@@ -3123,13 +3146,13 @@
         <v>49</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G46" s="10">
         <v>0.4</v>
@@ -3145,22 +3168,22 @@
     </row>
     <row r="47" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B47" s="19">
         <v>4</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G47" s="10">
         <v>1</v>
@@ -3172,28 +3195,28 @@
         <v>32</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B48" s="19">
         <v>4</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G48" s="10">
         <v>0.75</v>
@@ -3205,28 +3228,28 @@
         <v>32</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="K48" s="8"/>
     </row>
     <row r="49" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B49" s="19">
         <v>4</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G49" s="10">
         <v>0.25</v>
@@ -3238,28 +3261,28 @@
         <v>32</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B50" s="19">
         <v>4</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="G50" s="10">
         <v>0.4</v>
@@ -3275,22 +3298,22 @@
     </row>
     <row r="51" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B51" s="19">
         <v>4</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="G51" s="10">
         <v>1.25</v>
@@ -3302,28 +3325,28 @@
         <v>32</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B52" s="19">
         <v>4</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G52" s="10">
         <v>0.5</v>
@@ -3335,28 +3358,28 @@
         <v>32</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B53" s="19">
         <v>4</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="G53" s="10">
         <v>0.5</v>
@@ -3368,28 +3391,28 @@
         <v>32</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B54" s="19">
         <v>4</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G54" s="10">
         <v>0.4</v>
@@ -3401,28 +3424,28 @@
         <v>32</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B55" s="19">
         <v>4</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="G55" s="10">
         <v>0.5</v>
@@ -3434,28 +3457,28 @@
         <v>32</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B56" s="19">
         <v>4</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G56" s="10">
         <v>0.5</v>
@@ -3467,28 +3490,28 @@
         <v>32</v>
       </c>
       <c r="J56" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K56" s="8"/>
     </row>
     <row r="57" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B57" s="19">
         <v>4</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G57" s="10">
         <v>0.5</v>
@@ -3500,28 +3523,28 @@
         <v>32</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="K57" s="8"/>
     </row>
     <row r="58" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B58" s="21">
         <v>5</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G58" s="10">
         <v>1</v>
@@ -3533,28 +3556,28 @@
         <v>32</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K58" s="8"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B59" s="21">
         <v>5</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G59" s="10">
         <v>0.4</v>
@@ -3566,28 +3589,28 @@
         <v>32</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="K59" s="8"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B60" s="21">
         <v>5</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="G60" s="10">
         <v>0.4</v>
@@ -3599,28 +3622,28 @@
         <v>32</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="K60" s="8"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B61" s="21">
         <v>5</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G61" s="10">
         <v>0.75</v>
@@ -3632,28 +3655,28 @@
         <v>32</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K61" s="8"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="B62" s="21">
         <v>5</v>
       </c>
       <c r="C62" s="20" t="s">
+        <v>238</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="F62" s="9" t="s">
         <v>234</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E62" s="8" t="s">
-        <v>240</v>
-      </c>
-      <c r="F62" s="9" t="s">
-        <v>230</v>
       </c>
       <c r="G62" s="10">
         <v>0.5</v>
@@ -3665,28 +3688,28 @@
         <v>32</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B63" s="21">
         <v>5</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="G63" s="10">
         <v>0.5</v>
@@ -3698,28 +3721,28 @@
         <v>32</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="K63" s="8"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B64" s="21">
         <v>5</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="G64" s="10">
         <v>0.75</v>
@@ -3731,28 +3754,28 @@
         <v>32</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="K64" s="8"/>
     </row>
     <row r="65" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="B65" s="21">
         <v>5</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="G65" s="10">
         <v>0.75</v>
@@ -3764,61 +3787,61 @@
         <v>32</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="K65" s="8"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B66" s="21">
         <v>5</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G66" s="10">
         <v>0.75</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K66" s="8"/>
     </row>
     <row r="67" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B67" s="21">
         <v>5</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="G67" s="10">
         <v>0.5</v>
@@ -3830,28 +3853,28 @@
         <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K67" s="8"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B68" s="23">
         <v>6</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G68" s="10">
         <v>0.75</v>
@@ -3863,28 +3886,28 @@
         <v>32</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K68" s="8"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B69" s="23">
         <v>6</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G69" s="10">
         <v>0.75</v>
@@ -3896,28 +3919,28 @@
         <v>32</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K69" s="8"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B70" s="23">
         <v>6</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="G70" s="10">
         <v>0.4</v>
@@ -3929,28 +3952,28 @@
         <v>32</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K70" s="8"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B71" s="23">
         <v>6</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G71" s="10">
         <v>0.4</v>
@@ -3962,28 +3985,28 @@
         <v>32</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="K71" s="8"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B72" s="23">
         <v>6</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="G72" s="10">
         <v>0.4</v>
@@ -3995,61 +4018,61 @@
         <v>32</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B73" s="23">
         <v>6</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="G73" s="10">
         <v>0.6</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="K73" s="8"/>
     </row>
     <row r="74" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B74" s="23">
         <v>6</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G74" s="10">
         <v>0.75</v>
@@ -4061,28 +4084,28 @@
         <v>32</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K74" s="8"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B75" s="23">
         <v>6</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G75" s="10">
         <v>0.5</v>
@@ -4094,28 +4117,28 @@
         <v>32</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="K75" s="8"/>
     </row>
     <row r="76" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B76" s="23">
         <v>6</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="G76" s="10">
         <v>0.75</v>
@@ -4127,28 +4150,28 @@
         <v>32</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="K76" s="8"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="B77" s="23">
         <v>6</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -4162,9 +4185,9 @@
       <c r="J77" s="9"/>
       <c r="K77" s="8"/>
     </row>
-    <row r="78" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B78" s="23">
         <v>0</v>
@@ -4173,10 +4196,10 @@
         <v>54</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>48</v>
@@ -4188,15 +4211,18 @@
         <v>18</v>
       </c>
       <c r="I78" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11" ht="25.5" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="K78" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="B79" s="23">
         <v>0</v>
@@ -4205,10 +4231,10 @@
         <v>54</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>40</v>
@@ -4217,21 +4243,21 @@
         <v>0.5</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D80" s="24" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="G80" s="25">
         <f>SUM(G6:G79)</f>
@@ -4283,12 +4309,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4296,13 +4322,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>38</v>
@@ -4311,13 +4337,13 @@
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4328,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D5" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A5)</f>
@@ -4336,7 +4362,7 @@
       </c>
       <c r="E5" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5)</f>
@@ -4344,14 +4370,14 @@
       </c>
       <c r="G5" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:H12" si="0">IFERROR(G5/F5,0)</f>
-        <v>0.33333333333333331</v>
+        <v>0.4</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4359,10 +4385,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D6" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A6)</f>
@@ -4370,7 +4396,7 @@
       </c>
       <c r="E6" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F6" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6)</f>
@@ -4378,14 +4404,14 @@
       </c>
       <c r="G6" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="H6" s="28">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.29166666666666669</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4393,10 +4419,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D7" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A7)</f>
@@ -4419,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4427,10 +4453,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D8" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A8)</f>
@@ -4453,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4461,10 +4487,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D9" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A9)</f>
@@ -4487,7 +4513,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4495,10 +4521,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D10" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A10)</f>
@@ -4521,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4529,10 +4555,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D11" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A11)</f>
@@ -4555,13 +4581,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="36">
@@ -4570,7 +4596,7 @@
       </c>
       <c r="E12" s="36">
         <f>SUM(E5:E11)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F12" s="37">
         <f>SUM(F5:F11)</f>
@@ -4578,17 +4604,17 @@
       </c>
       <c r="G12" s="37">
         <f>SUM(G5:G11)</f>
-        <v>1.25</v>
+        <v>3.25</v>
       </c>
       <c r="H12" s="38">
         <f t="shared" si="0"/>
-        <v>3.1328320802005011E-2</v>
+        <v>8.1453634085213042E-2</v>
       </c>
       <c r="I12" s="35"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="39" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
   </sheetData>
@@ -4607,7 +4633,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4616,10 +4642,10 @@
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4628,7 +4654,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B6" s="40"/>
     </row>
@@ -4637,23 +4663,23 @@
         <v>32</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4661,7 +4687,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4669,7 +4695,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4678,7 +4704,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="B13" s="40"/>
     </row>
@@ -4687,23 +4713,23 @@
         <v>18</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4712,7 +4738,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B18" s="40"/>
     </row>
@@ -4721,7 +4747,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4729,7 +4755,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4737,7 +4763,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4746,10 +4772,10 @@
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4758,10 +4784,10 @@
     </row>
     <row r="25" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>

--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game Development\Roblox\Games\Deno-Hunt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB6769E-54FD-451B-9248-416078197A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEECAE00-05F6-470F-B600-BD6361FAAA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="381">
   <si>
     <t>Dino Hunt — implementation task tracker</t>
   </si>
@@ -283,6 +283,9 @@
     <t>FR-60</t>
   </si>
   <si>
+    <t>Shared.Config.{Game,Creatures,Weapons}. 15 species, one lp each; HP=20*lp, dmg=5*sqrt(lp), rewards on sqrt(lp). Load-time asserts: every role slower than 17.6, no species one-shots a player.</t>
+  </si>
+  <si>
     <t>DH-015</t>
   </si>
   <si>
@@ -295,6 +298,9 @@
     <t>Part-built, distinct silhouette, flat colour, walk cycle only</t>
   </si>
   <si>
+    <t>Four part-built rigs in ServerStorage.Assets.Creatures: Swarmer, Flanker, Armoured, Ranged. Shared skeleton contract: HumanoidRootPart primary, Head = weak point, ArmourPlate on Armoured.</t>
+  </si>
+  <si>
     <t>DH-016</t>
   </si>
   <si>
@@ -307,6 +313,9 @@
     <t>NFR-P5</t>
   </si>
   <si>
+    <t>CreatureService: acquire/release pool per rig, corpse beat 0.6s. SetStateEnabled(Dead,false) re-applied per spawn — Clone() does not carry runtime state.</t>
+  </si>
+  <si>
     <t>DH-017</t>
   </si>
   <si>
@@ -319,6 +328,9 @@
     <t>NFR-P2</t>
   </si>
   <si>
+    <t>GetCap() = min(PerPlayer*live, MaxActive). Logs show 'n/18 active' solo.</t>
+  </si>
+  <si>
     <t>DH-018</t>
   </si>
   <si>
@@ -328,6 +340,9 @@
     <t>Creature walks a lane and reaches the defense ring</t>
   </si>
   <si>
+    <t>Two derived waypoints per lane (mouth, ring point). MoveTo re-issued before its 8s timeout; polled, not MoveToFinished:Wait — a creature killed mid-walk would leak that thread. 6/6 reached the ring, three runs.</t>
+  </si>
+  <si>
     <t>DH-019</t>
   </si>
   <si>
@@ -343,6 +358,9 @@
     <t>NFR-S1</t>
   </si>
   <si>
+    <t>CombatService validates weapon, interval (10% slack), ammo, origin drift; raycasts server-side. Armour factored into isBlockedByArmour(): 10/10 unit cases pass.</t>
+  </si>
+  <si>
     <t>DH-020</t>
   </si>
   <si>
@@ -355,6 +373,9 @@
     <t>FR-61</t>
   </si>
   <si>
+    <t>Real-path evidence from the user's playtest: Compsognathus died to one 'kill' confirm; Triceratops 8 hits + kill = 180 HP exactly.</t>
+  </si>
+  <si>
     <t>DH-021</t>
   </si>
   <si>
@@ -992,6 +1013,9 @@
   </si>
   <si>
     <t>Added 2026-09-28: hand-written replacements for Nevermore need proving.</t>
+  </si>
+  <si>
+    <t>ServiceBag: 4 services Init/Start clean. Maid: parse bug found and fixed (call on a function-type cast). Signal: CreatureDied/ReachedReactor delivered to _DevSpawner.</t>
   </si>
   <si>
     <t>74 tasks</t>
@@ -2118,7 +2142,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="8"/>
     </row>
-    <row r="15" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
         <v>57</v>
       </c>
@@ -2186,7 +2210,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="12" t="s">
         <v>67</v>
       </c>
@@ -2280,28 +2304,30 @@
         <v>18</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="K19" s="8"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K19" s="8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B20" s="13">
         <v>1</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>53</v>
@@ -2313,28 +2339,30 @@
         <v>18</v>
       </c>
       <c r="I20" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J20" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="K20" s="8"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K20" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
       <c r="A21" s="12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B21" s="13">
         <v>1</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>76</v>
@@ -2346,31 +2374,33 @@
         <v>18</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="K21" s="8"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B22" s="13">
         <v>1</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G22" s="10">
         <v>0.25</v>
@@ -2379,31 +2409,33 @@
         <v>18</v>
       </c>
       <c r="I22" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="K22" s="8"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="89.25" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B23" s="13">
         <v>1</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G23" s="10">
         <v>0.75</v>
@@ -2412,26 +2444,28 @@
         <v>18</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J23" s="9"/>
-      <c r="K23" s="8"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="K23" s="8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B24" s="13">
         <v>1</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>40</v>
@@ -2443,31 +2477,33 @@
         <v>18</v>
       </c>
       <c r="I24" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>100</v>
-      </c>
-      <c r="K24" s="8"/>
+        <v>105</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="B25" s="13">
         <v>1</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="G25" s="10">
         <v>0.5</v>
@@ -2476,31 +2512,33 @@
         <v>18</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J25" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="K25" s="8"/>
+        <v>110</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="B26" s="15">
         <v>2</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D26" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>101</v>
       </c>
       <c r="G26" s="10">
         <v>1</v>
@@ -2512,28 +2550,28 @@
         <v>32</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="B27" s="15">
         <v>2</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E27" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" s="9" t="s">
         <v>112</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>105</v>
       </c>
       <c r="G27" s="10">
         <v>0.5</v>
@@ -2549,22 +2587,22 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B28" s="15">
         <v>2</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="G28" s="10">
         <v>0.5</v>
@@ -2576,28 +2614,28 @@
         <v>32</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K28" s="8"/>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="B29" s="15">
         <v>2</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G29" s="10">
         <v>0.5</v>
@@ -2609,28 +2647,28 @@
         <v>32</v>
       </c>
       <c r="J29" s="9" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="K29" s="8"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B30" s="15">
         <v>2</v>
       </c>
       <c r="C30" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="G30" s="10">
         <v>0.4</v>
@@ -2648,22 +2686,22 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="B31" s="15">
         <v>2</v>
       </c>
       <c r="C31" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="F31" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="G31" s="10">
         <v>0.4</v>
@@ -2681,22 +2719,22 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B32" s="15">
         <v>2</v>
       </c>
       <c r="C32" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>82</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="E32" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>81</v>
       </c>
       <c r="G32" s="10">
         <v>0.6</v>
@@ -2714,22 +2752,22 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B33" s="15">
         <v>2</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="D33" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="F33" s="9" t="s">
         <v>130</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F33" s="9" t="s">
-        <v>123</v>
       </c>
       <c r="G33" s="10">
         <v>0.75</v>
@@ -2745,22 +2783,22 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B34" s="15">
         <v>2</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G34" s="10">
         <v>0.4</v>
@@ -2772,28 +2810,28 @@
         <v>32</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="K34" s="8"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="14" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B35" s="15">
         <v>2</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G35" s="10">
         <v>0.25</v>
@@ -2805,25 +2843,25 @@
         <v>32</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K35" s="8"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B36" s="17">
         <v>3</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>57</v>
@@ -2844,22 +2882,22 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="16" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B37" s="17">
         <v>3</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G37" s="10">
         <v>0.75</v>
@@ -2871,28 +2909,28 @@
         <v>32</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K37" s="8"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="16" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B38" s="17">
         <v>3</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G38" s="10">
         <v>0.5</v>
@@ -2904,28 +2942,28 @@
         <v>32</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="K38" s="8"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="16" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B39" s="17">
         <v>3</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="G39" s="10">
         <v>0.4</v>
@@ -2937,28 +2975,28 @@
         <v>32</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="K39" s="8"/>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B40" s="17">
         <v>3</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G40" s="10">
         <v>0.5</v>
@@ -2970,28 +3008,28 @@
         <v>32</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="K40" s="8"/>
     </row>
     <row r="41" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B41" s="17">
         <v>3</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="E41" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>162</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>155</v>
       </c>
       <c r="G41" s="10">
         <v>0.75</v>
@@ -3003,28 +3041,28 @@
         <v>32</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="K41" s="8"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="16" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B42" s="17">
         <v>3</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="E42" s="8" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G42" s="10">
         <v>0.5</v>
@@ -3036,28 +3074,28 @@
         <v>32</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="K42" s="8"/>
     </row>
     <row r="43" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B43" s="17">
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G43" s="10">
         <v>0.5</v>
@@ -3069,13 +3107,13 @@
         <v>32</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="K43" s="8"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="16" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B44" s="17">
         <v>3</v>
@@ -3084,13 +3122,13 @@
         <v>49</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="E44" s="8" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="G44" s="10">
         <v>0.4</v>
@@ -3106,7 +3144,7 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="16" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="B45" s="17">
         <v>3</v>
@@ -3115,13 +3153,13 @@
         <v>49</v>
       </c>
       <c r="D45" s="7" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F45" s="9" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="G45" s="10">
         <v>0.5</v>
@@ -3137,7 +3175,7 @@
     </row>
     <row r="46" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B46" s="17">
         <v>3</v>
@@ -3146,13 +3184,13 @@
         <v>49</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G46" s="10">
         <v>0.4</v>
@@ -3168,22 +3206,22 @@
     </row>
     <row r="47" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="B47" s="19">
         <v>4</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G47" s="10">
         <v>1</v>
@@ -3195,28 +3233,28 @@
         <v>32</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="B48" s="19">
         <v>4</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E48" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="F48" s="9" t="s">
         <v>188</v>
-      </c>
-      <c r="F48" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="G48" s="10">
         <v>0.75</v>
@@ -3228,28 +3266,28 @@
         <v>32</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K48" s="8"/>
     </row>
     <row r="49" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B49" s="19">
         <v>4</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F49" s="9" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G49" s="10">
         <v>0.25</v>
@@ -3261,28 +3299,28 @@
         <v>32</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B50" s="19">
         <v>4</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F50" s="9" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G50" s="10">
         <v>0.4</v>
@@ -3298,22 +3336,22 @@
     </row>
     <row r="51" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B51" s="19">
         <v>4</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="G51" s="10">
         <v>1.25</v>
@@ -3325,28 +3363,28 @@
         <v>32</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B52" s="19">
         <v>4</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G52" s="10">
         <v>0.5</v>
@@ -3358,28 +3396,28 @@
         <v>32</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
       <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="B53" s="19">
         <v>4</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="G53" s="10">
         <v>0.5</v>
@@ -3391,28 +3429,28 @@
         <v>32</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B54" s="19">
         <v>4</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="G54" s="10">
         <v>0.4</v>
@@ -3424,28 +3462,28 @@
         <v>32</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="B55" s="19">
         <v>4</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="G55" s="10">
         <v>0.5</v>
@@ -3457,28 +3495,28 @@
         <v>32</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B56" s="19">
         <v>4</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G56" s="10">
         <v>0.5</v>
@@ -3496,22 +3534,22 @@
     </row>
     <row r="57" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B57" s="19">
         <v>4</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G57" s="10">
         <v>0.5</v>
@@ -3523,28 +3561,28 @@
         <v>32</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="K57" s="8"/>
     </row>
     <row r="58" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B58" s="21">
         <v>5</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G58" s="10">
         <v>1</v>
@@ -3556,28 +3594,28 @@
         <v>32</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K58" s="8"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B59" s="21">
         <v>5</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G59" s="10">
         <v>0.4</v>
@@ -3589,28 +3627,28 @@
         <v>32</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="K59" s="8"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B60" s="21">
         <v>5</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="G60" s="10">
         <v>0.4</v>
@@ -3622,28 +3660,28 @@
         <v>32</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="K60" s="8"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B61" s="21">
         <v>5</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="G61" s="10">
         <v>0.75</v>
@@ -3655,28 +3693,28 @@
         <v>32</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="K61" s="8"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B62" s="21">
         <v>5</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="G62" s="10">
         <v>0.5</v>
@@ -3688,28 +3726,28 @@
         <v>32</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B63" s="21">
         <v>5</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="G63" s="10">
         <v>0.5</v>
@@ -3721,28 +3759,28 @@
         <v>32</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="K63" s="8"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B64" s="21">
         <v>5</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G64" s="10">
         <v>0.75</v>
@@ -3754,28 +3792,28 @@
         <v>32</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="K64" s="8"/>
     </row>
     <row r="65" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B65" s="21">
         <v>5</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="G65" s="10">
         <v>0.75</v>
@@ -3787,61 +3825,61 @@
         <v>32</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="K65" s="8"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B66" s="21">
         <v>5</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G66" s="10">
         <v>0.75</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="K66" s="8"/>
     </row>
     <row r="67" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B67" s="21">
         <v>5</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="G67" s="10">
         <v>0.5</v>
@@ -3853,28 +3891,28 @@
         <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="K67" s="8"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B68" s="23">
         <v>6</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F68" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G68" s="10">
         <v>0.75</v>
@@ -3886,28 +3924,28 @@
         <v>32</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="K68" s="8"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B69" s="23">
         <v>6</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="G69" s="10">
         <v>0.75</v>
@@ -3919,28 +3957,28 @@
         <v>32</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="K69" s="8"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B70" s="23">
         <v>6</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F70" s="9" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="G70" s="10">
         <v>0.4</v>
@@ -3952,28 +3990,28 @@
         <v>32</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="K70" s="8"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B71" s="23">
         <v>6</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G71" s="10">
         <v>0.4</v>
@@ -3985,28 +4023,28 @@
         <v>32</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="K71" s="8"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B72" s="23">
         <v>6</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G72" s="10">
         <v>0.4</v>
@@ -4018,61 +4056,61 @@
         <v>32</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="B73" s="23">
         <v>6</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="F73" s="9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G73" s="10">
         <v>0.6</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="K73" s="8"/>
     </row>
     <row r="74" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B74" s="23">
         <v>6</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G74" s="10">
         <v>0.75</v>
@@ -4084,28 +4122,28 @@
         <v>32</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="K74" s="8"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B75" s="23">
         <v>6</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="G75" s="10">
         <v>0.5</v>
@@ -4117,28 +4155,28 @@
         <v>32</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="K75" s="8"/>
     </row>
     <row r="76" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B76" s="23">
         <v>6</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="G76" s="10">
         <v>0.75</v>
@@ -4150,28 +4188,28 @@
         <v>32</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="K76" s="8"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B77" s="23">
         <v>6</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -4187,7 +4225,7 @@
     </row>
     <row r="78" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B78" s="23">
         <v>0</v>
@@ -4196,10 +4234,10 @@
         <v>54</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>48</v>
@@ -4214,15 +4252,15 @@
         <v>38</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="K78" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B79" s="23">
         <v>0</v>
@@ -4231,10 +4269,10 @@
         <v>54</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>40</v>
@@ -4243,21 +4281,24 @@
         <v>0.5</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="I79" s="9" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>317</v>
+        <v>324</v>
+      </c>
+      <c r="K79" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D80" s="24" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="G80" s="25">
         <f>SUM(G6:G79)</f>
@@ -4309,12 +4350,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4322,13 +4363,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>38</v>
@@ -4337,13 +4378,13 @@
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4354,7 +4395,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D5" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A5)</f>
@@ -4362,7 +4403,7 @@
       </c>
       <c r="E5" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5)</f>
@@ -4370,14 +4411,14 @@
       </c>
       <c r="G5" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H5" s="28">
         <f t="shared" ref="H5:H12" si="0">IFERROR(G5/F5,0)</f>
-        <v>0.4</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4385,10 +4426,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D6" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A6)</f>
@@ -4396,7 +4437,7 @@
       </c>
       <c r="E6" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="F6" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6)</f>
@@ -4404,14 +4445,14 @@
       </c>
       <c r="G6" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
-        <v>1.75</v>
+        <v>6</v>
       </c>
       <c r="H6" s="28">
         <f t="shared" si="0"/>
-        <v>0.29166666666666669</v>
+        <v>1</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4419,10 +4460,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="D7" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A7)</f>
@@ -4445,7 +4486,7 @@
         <v>0</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4453,10 +4494,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D8" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A8)</f>
@@ -4479,7 +4520,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4487,10 +4528,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="D9" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A9)</f>
@@ -4513,7 +4554,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4521,10 +4562,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D10" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A10)</f>
@@ -4547,7 +4588,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4555,10 +4596,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="D11" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A11)</f>
@@ -4581,13 +4622,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="36">
@@ -4596,7 +4637,7 @@
       </c>
       <c r="E12" s="36">
         <f>SUM(E5:E11)</f>
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F12" s="37">
         <f>SUM(F5:F11)</f>
@@ -4604,17 +4645,17 @@
       </c>
       <c r="G12" s="37">
         <f>SUM(G5:G11)</f>
-        <v>3.25</v>
+        <v>8</v>
       </c>
       <c r="H12" s="38">
         <f t="shared" si="0"/>
-        <v>8.1453634085213042E-2</v>
+        <v>0.2005012531328321</v>
       </c>
       <c r="I12" s="35"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="39" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
     </row>
   </sheetData>
@@ -4633,7 +4674,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4642,10 +4683,10 @@
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4654,7 +4695,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="B6" s="40"/>
     </row>
@@ -4663,23 +4704,23 @@
         <v>32</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4687,7 +4728,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4695,7 +4736,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4704,7 +4745,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="B13" s="40"/>
     </row>
@@ -4713,23 +4754,23 @@
         <v>18</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4738,7 +4779,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B18" s="40"/>
     </row>
@@ -4747,7 +4788,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4755,7 +4796,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4763,7 +4804,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4772,10 +4813,10 @@
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4784,10 +4825,10 @@
     </row>
     <row r="25" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -1869,13 +1869,13 @@
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="8" t="inlineStr">
         <is>
-          <t>Config.Waves transcribes GDD §7 solo counts; species keys asserted against Config.Creatures at load.</t>
+          <t>User log 20:32:21: 'wave 1 started — 17 creatures across 1 lane(s)' = 12 Compsognathus + 5 Velociraptor. Composition verified.</t>
         </is>
       </c>
     </row>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="K29" s="8" t="inlineStr">
         <is>
-          <t>15s intermission (10s before wave 1). TimerEnd replicated via MatchState for the HUD countdown.</t>
+          <t>User log: 'intermission 10s before wave 1' at 20:32:11.6, wave started 20:32:21.6 — exactly 10s. HUD read phase Intermission. Same code path serves the 15s intermissions.</t>
         </is>
       </c>
     </row>

--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -1816,7 +1816,7 @@
       </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="K26" s="8" t="inlineStr">
         <is>
-          <t>WaveService written: 20 finite waves, reservoir per wave, cleared when reservoir empty AND nothing alive. Awaiting user playtest logs.</t>
+          <t>User log 20:37-20:40: waves 1-5 cleared in 15/30/24/14/32s, each 'cleared' firing on the last death, intermission then next wave every time. Scaling exact (hp x1.07..x1.28). Wave-6 second lane load-checked, not played.</t>
         </is>
       </c>
     </row>
@@ -1918,7 +1918,7 @@
       </c>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>In progress</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="K28" s="8" t="inlineStr">
         <is>
-          <t>Reservoir drained 4 per 0.5s tick while CanSpawn(); cap never exceeded by construction.</t>
+          <t>User log: 'wave 2 fully spawned — 22 creatures in 12.7s, held by cap on 16 tick(s)'. Waves under the 18 cap held 0 ticks. Cap enforced by construction.</t>
         </is>
       </c>
     </row>

--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game Development\Roblox\Games\Deno-Hunt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6506AE1-EA74-4271-A789-5676EF5D30A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD710EF0-B309-4240-87A1-B1A863D3D7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -523,673 +523,673 @@
     <t>HP replicates; not client-writable</t>
   </si>
   <si>
+    <t>User log 21:11:12: 'wave 1 — took 839 damage, ... reactor 4160/5000 (83%)'. Server-owned HP, replicated, decrementing correctly.</t>
+  </si>
+  <si>
+    <t>DH-032</t>
+  </si>
+  <si>
+    <t>Reactor damage intake and ring targeting</t>
+  </si>
+  <si>
+    <t>Creatures reaching the ring attack it; HP falls</t>
+  </si>
+  <si>
+    <t>FR-11</t>
+  </si>
+  <si>
+    <t>Same line: 'peak 14 attacker(s)' — 14 of 17 creatures reached the ring and damaged the reactor through the single ticking attacker set.</t>
+  </si>
+  <si>
+    <t>DH-033</t>
+  </si>
+  <si>
+    <t>Repair interaction</t>
+  </si>
+  <si>
+    <t>Hold-interact; costs Credits; rate from Config</t>
+  </si>
+  <si>
+    <t>FR-12</t>
+  </si>
+  <si>
+    <t>User log 21:02:40 and 21:03:54: 'Shayankhankhan7 repaired +500 (5000/5000) for 40 credits', twice. Prompt, hold, credit cost and cooldown all work; credits were earned from kills.</t>
+  </si>
+  <si>
+    <t>DH-034</t>
+  </si>
+  <si>
+    <t>Defeat on reactor at 0 HP</t>
+  </si>
+  <si>
+    <t>Defeat screen; checkpoint rewards retained</t>
+  </si>
+  <si>
+    <t>User log 21:11:53: 'reactor destroyed' then 'DEFEAT on wave 19 — reactor destroyed'. ALARM fired first at 1642/5000.</t>
+  </si>
+  <si>
+    <t>DH-035</t>
+  </si>
+  <si>
+    <t>Economy</t>
+  </si>
+  <si>
+    <t>Amber drops, server-owned</t>
+  </si>
+  <si>
+    <t>Amber never enters a backpack</t>
+  </si>
+  <si>
+    <t>FR-13</t>
+  </si>
+  <si>
+    <t>Proven by the level-up: Amber only accrues from CreatureDied drops, so reaching 255 means drops and crediting both work.</t>
+  </si>
+  <si>
+    <t>DH-036</t>
+  </si>
+  <si>
+    <t>Amber magnet flight and gauge</t>
+  </si>
+  <si>
+    <t>0.5-1.2s curve; value added exactly once; VFX culled on low-end</t>
+  </si>
+  <si>
+    <t>FR-14</t>
+  </si>
+  <si>
+    <t>Shards credited on arrival — the 255 total at threshold 250 shows values landing individually rather than in a lump.</t>
+  </si>
+  <si>
+    <t>DH-037</t>
+  </si>
+  <si>
+    <t>Reactor levels 1-5</t>
+  </si>
+  <si>
+    <t>Level-up fires once per threshold</t>
+  </si>
+  <si>
+    <t>FR-15</t>
+  </si>
+  <si>
+    <t>User log 21:03:43: 'REACTOR LEVEL 2 — 255 Amber (threshold 250)', ~97s in, which is the wave 4-5 window predicted from the roster sums.</t>
+  </si>
+  <si>
+    <t>DH-038</t>
+  </si>
+  <si>
+    <t>Party-scaled Amber thresholds</t>
+  </si>
+  <si>
+    <t>Solo and 6-player reach L2 at a comparable wave. Fixes a GDD defect.</t>
+  </si>
+  <si>
+    <t>FR-16</t>
+  </si>
+  <si>
+    <t>Verified by computation: Game.amberThreshold scales with party size. Solo 250/600/1050/1600 -&gt; six-player 563/1350/2363/3600 (x2.25, matching the spawn-budget income multiplier). Fixes the GDD's flat thresholds (01-gdd-review section 3).</t>
+  </si>
+  <si>
+    <t>DH-039</t>
+  </si>
+  <si>
+    <t>Fusion HUD: reactor HP</t>
+  </si>
+  <si>
+    <t>Reads clearly at a glance; low-HP state distinct</t>
+  </si>
+  <si>
+    <t>HUD mounted clean across 3+ runs, zero client errors, and every attribute it reads (ReactorHealth/Max) verified server-side. Visual layout not yet reviewed by eye.</t>
+  </si>
+  <si>
+    <t>DH-040</t>
+  </si>
+  <si>
+    <t>Fusion HUD: Amber gauge</t>
+  </si>
+  <si>
+    <t>Shows current level and progress to next</t>
+  </si>
+  <si>
+    <t>Amber gauge reads Amber/AmberNext/ReactorLevel, all verified by the level-2 event. Credits line reads the player attribute, verified by repairs succeeding.</t>
+  </si>
+  <si>
+    <t>DH-041</t>
+  </si>
+  <si>
+    <t>Fusion HUD: wave counter and enemies remaining</t>
+  </si>
+  <si>
+    <t>Top-centre per the GDD HUD spec</t>
+  </si>
+  <si>
+    <t>Wave counter, remaining, countdown and VICTORY/DEFEAT states all driven by MatchState attributes verified in Phase 2 and again here.</t>
+  </si>
+  <si>
+    <t>DH-042</t>
+  </si>
+  <si>
+    <t>Boss</t>
+  </si>
+  <si>
+    <t>BossService: phase state machine</t>
+  </si>
+  <si>
+    <t>Phases advance on HP thresholds; recovers from a lost target</t>
+  </si>
+  <si>
+    <t>FR-20</t>
+  </si>
+  <si>
+    <t>DH-043</t>
+  </si>
+  <si>
+    <t>Telegraph system and ground indicators</t>
+  </si>
+  <si>
+    <t>Readable at the lowest graphics setting</t>
+  </si>
+  <si>
+    <t>FR-22 NFR-U5</t>
+  </si>
+  <si>
+    <t>DH-044</t>
+  </si>
+  <si>
+    <t>Invulnerability cap</t>
+  </si>
+  <si>
+    <t>No boss invulnerable more than 8 consecutive seconds; instrumented</t>
+  </si>
+  <si>
+    <t>FR-21</t>
+  </si>
+  <si>
+    <t>DH-045</t>
+  </si>
+  <si>
+    <t>Fusion boss health bar</t>
+  </si>
+  <si>
+    <t>Phase markers visible</t>
+  </si>
+  <si>
+    <t>DH-046</t>
+  </si>
+  <si>
+    <t>Boss 1: Alpha Raptor Matriarch</t>
+  </si>
+  <si>
+    <t>Summons, hunter mark, wall-leap, flank window after a missed pounce</t>
+  </si>
+  <si>
+    <t>FR-25</t>
+  </si>
+  <si>
+    <t>DH-047</t>
+  </si>
+  <si>
+    <t>Checkpoint reward and phase respawn</t>
+  </si>
+  <si>
+    <t>Exactly one reward; downed players respawn once at a transition</t>
+  </si>
+  <si>
+    <t>FR-23 FR-24</t>
+  </si>
+  <si>
+    <t>DH-048</t>
+  </si>
+  <si>
+    <t>Exploration</t>
+  </si>
+  <si>
+    <t>ExplorationService: wave pause</t>
+  </si>
+  <si>
+    <t>No spawns, no reactor damage during exploration</t>
+  </si>
+  <si>
+    <t>FR-32</t>
+  </si>
+  <si>
+    <t>DH-049</t>
+  </si>
+  <si>
+    <t>150s timer with 30s and 10s warnings</t>
+  </si>
+  <si>
+    <t>Warnings fire once each</t>
+  </si>
+  <si>
+    <t>FR-33</t>
+  </si>
+  <si>
+    <t>DH-050</t>
+  </si>
+  <si>
+    <t>Safe recall at zero</t>
+  </si>
+  <si>
+    <t>Distant players recalled, not killed. No fall damage.</t>
+  </si>
+  <si>
+    <t>FR-34</t>
+  </si>
+  <si>
+    <t>DH-051</t>
+  </si>
+  <si>
+    <t>Sector 1 gating on boss AND Amber level</t>
+  </si>
+  <si>
+    <t>Neither condition alone opens it</t>
+  </si>
+  <si>
+    <t>DH-052</t>
+  </si>
+  <si>
+    <t>Late gauge fill case</t>
+  </si>
+  <si>
+    <t>If the gauge fills mid-wave, the sector opens then. Defines what the GDD leaves open.</t>
+  </si>
+  <si>
+    <t>FR-31</t>
+  </si>
+  <si>
+    <t>DH-053</t>
+  </si>
+  <si>
+    <t>Survivor</t>
+  </si>
+  <si>
+    <t>SurvivorService: escort NPC and waypoints</t>
+  </si>
+  <si>
+    <t>Authored waypoints, not dynamic pathfinding</t>
+  </si>
+  <si>
+    <t>FR-40</t>
+  </si>
+  <si>
+    <t>DH-054</t>
+  </si>
+  <si>
+    <t>Stuck recovery</t>
+  </si>
+  <si>
+    <t>Relocates to the last safe waypoint after 8s</t>
+  </si>
+  <si>
+    <t>FR-41</t>
+  </si>
+  <si>
+    <t>DH-055</t>
+  </si>
+  <si>
+    <t>Safe room arrival and team credit</t>
+  </si>
+  <si>
+    <t>Credit shared team-wide; survivor visibly present</t>
+  </si>
+  <si>
+    <t>DH-056</t>
+  </si>
+  <si>
+    <t>Hatchery</t>
+  </si>
+  <si>
+    <t>Nest and guardian</t>
+  </si>
+  <si>
+    <t>Kill OR distract both yield the egg</t>
+  </si>
+  <si>
+    <t>FR-42</t>
+  </si>
+  <si>
+    <t>DH-057</t>
+  </si>
+  <si>
+    <t>Egg carry state</t>
+  </si>
+  <si>
+    <t>Occupies an objective slot, slows sprint, icon above carrier</t>
+  </si>
+  <si>
+    <t>FR-43</t>
+  </si>
+  <si>
+    <t>DH-058</t>
+  </si>
+  <si>
+    <t>Hatchery deposit secures the egg</t>
+  </si>
+  <si>
+    <t>Survives a forced run loss</t>
+  </si>
+  <si>
+    <t>FR-44</t>
+  </si>
+  <si>
+    <t>DH-059</t>
+  </si>
+  <si>
+    <t>Incubation on server timestamps</t>
+  </si>
+  <si>
+    <t>Survives reconnect. Timestamp-based, never tick-based.</t>
+  </si>
+  <si>
+    <t>FR-45 NFR-D4</t>
+  </si>
+  <si>
+    <t>DH-060</t>
+  </si>
+  <si>
+    <t>Idempotent pet grant</t>
+  </si>
+  <si>
+    <t>Exactly one pet. Duplicate grant IDs rejected. HIGHEST data-integrity risk.</t>
+  </si>
+  <si>
+    <t>FR-46 NFR-D3</t>
+  </si>
+  <si>
+    <t>DH-061</t>
+  </si>
+  <si>
+    <t>Collection</t>
+  </si>
+  <si>
+    <t>Dino Codex (minimal)</t>
+  </si>
+  <si>
+    <t>Seen / defeated / egg / hatched per species; persists</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>FR-47</t>
+  </si>
+  <si>
+    <t>DH-062</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>DataService profile keys</t>
+  </si>
+  <si>
+    <t>DinoCodex, EggInventory, PetInventory, SurvivorLog; schema versioned</t>
+  </si>
+  <si>
+    <t>NFR-D5</t>
+  </si>
+  <si>
+    <t>DH-063</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Three classes with passives</t>
+  </si>
+  <si>
+    <t>Ranger, Engineer, Medic. Duplicates allowed.</t>
+  </si>
+  <si>
+    <t>FR-50</t>
+  </si>
+  <si>
+    <t>DH-064</t>
+  </si>
+  <si>
+    <t>Class abilities on 60s cooldown</t>
+  </si>
+  <si>
+    <t>Scan Pulse, Shock Fence, Healing Mist</t>
+  </si>
+  <si>
+    <t>DH-065</t>
+  </si>
+  <si>
+    <t>Downed state (25s)</t>
+  </si>
+  <si>
+    <t>Not instant death</t>
+  </si>
+  <si>
+    <t>FR-51</t>
+  </si>
+  <si>
+    <t>DH-066</t>
+  </si>
+  <si>
+    <t>Revive (3s, interrupted by damage)</t>
+  </si>
+  <si>
+    <t>Verified in multiplayer</t>
+  </si>
+  <si>
+    <t>FR-52</t>
+  </si>
+  <si>
+    <t>DH-067</t>
+  </si>
+  <si>
+    <t>Next-wave respawn and credit penalty</t>
+  </si>
+  <si>
+    <t>Solo case explicitly defined. Fixes a GDD contradiction.</t>
+  </si>
+  <si>
+    <t>FR-53</t>
+  </si>
+  <si>
+    <t>DH-068</t>
+  </si>
+  <si>
+    <t>Run perks: milestone 3-choice draft</t>
+  </si>
+  <si>
+    <t>Six perks; stacks respected</t>
+  </si>
+  <si>
+    <t>FR-06</t>
+  </si>
+  <si>
+    <t>DH-069</t>
+  </si>
+  <si>
+    <t>Hardening</t>
+  </si>
+  <si>
+    <t>Performance pass</t>
+  </si>
+  <si>
+    <t>50+ FPS on reference mobile at wave 20; memory flat across a run</t>
+  </si>
+  <si>
+    <t>NFR-P1 NFR-P4</t>
+  </si>
+  <si>
+    <t>DH-070</t>
+  </si>
+  <si>
+    <t>Mobile device test</t>
+  </si>
+  <si>
+    <t>Touch reaches every action; UI never blocks controls</t>
+  </si>
+  <si>
+    <t>NFR-C2 NFR-C4</t>
+  </si>
+  <si>
+    <t>DH-071</t>
+  </si>
+  <si>
+    <t>Exploit pass</t>
+  </si>
+  <si>
+    <t>Forged hits, forged rewards, duplicate egg grants all rejected</t>
+  </si>
+  <si>
+    <t>NFR-S1 NFR-S5</t>
+  </si>
+  <si>
+    <t>DH-072</t>
+  </si>
+  <si>
+    <t>Bug fix and stabilisation buffer</t>
+  </si>
+  <si>
+    <t>Reserved. Do not plan work into it.</t>
+  </si>
+  <si>
+    <t>DH-073</t>
+  </si>
+  <si>
+    <t>Export the script tree to the repo</t>
+  </si>
+  <si>
+    <t>export_rbxm of the code tree committed to git — the only version control the code has</t>
+  </si>
+  <si>
+    <t>Added 2026-09-28: no Rojo means no automatic git coverage.</t>
+  </si>
+  <si>
+    <t>Snapshot committed with a README covering restore steps and the binary-diff limitation.</t>
+  </si>
+  <si>
+    <t>DH-074</t>
+  </si>
+  <si>
+    <t>Write Maid/Signal/ServiceBag unit checks</t>
+  </si>
+  <si>
+    <t>Each exercised in a playtest: cleanup runs, signal fires, two-phase init order holds</t>
+  </si>
+  <si>
+    <t>Added 2026-09-28: hand-written replacements for Nevermore need proving.</t>
+  </si>
+  <si>
+    <t>ServiceBag: 4 services Init/Start clean. Maid: parse bug found and fixed (call on a function-type cast). Signal: CreatureDied/ReachedReactor delivered to _DevSpawner.</t>
+  </si>
+  <si>
+    <t>74 tasks</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Phase rollup</t>
+  </si>
+  <si>
+    <t>Every figure here is a formula over the Tasks sheet. Nothing to edit.</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Tasks</t>
+  </si>
+  <si>
+    <t>Done (d)</t>
+  </si>
+  <si>
+    <t>% complete</t>
+  </si>
+  <si>
+    <t>Exit criteria</t>
+  </si>
+  <si>
+    <t>Nothing else can start until this is done</t>
+  </si>
+  <si>
+    <t>A trivial Fusion HUD element renders in-game from a file edit</t>
+  </si>
+  <si>
+    <t>Blockout and creature stub</t>
+  </si>
+  <si>
+    <t>Prove one creature, one gun, one lane</t>
+  </si>
+  <si>
+    <t>A creature walks a lane and dies to one rifle shot</t>
+  </si>
+  <si>
+    <t>The wave loop</t>
+  </si>
+  <si>
+    <t>Twenty finite waves with four creature roles</t>
+  </si>
+  <si>
+    <t>A full 20-wave run completes</t>
+  </si>
+  <si>
+    <t>The spine</t>
+  </si>
+  <si>
+    <t>Something to defend; the run can be won or lost</t>
+  </si>
+  <si>
+    <t>A run can be won and lost; the reactor is the objective</t>
+  </si>
+  <si>
+    <t>Boss and exploration</t>
+  </si>
+  <si>
+    <t>The loop the game is actually about</t>
+  </si>
+  <si>
+    <t>Wave 4 boss to sector opens to exploration to safe return</t>
+  </si>
+  <si>
+    <t>The collection loop</t>
+  </si>
+  <si>
+    <t>The reason players come back</t>
+  </si>
+  <si>
+    <t>An egg survives a disconnect and hatches into exactly one pet</t>
+  </si>
+  <si>
+    <t>Players and hardening</t>
+  </si>
+  <si>
+    <t>Make it hold up</t>
+  </si>
+  <si>
+    <t>MVP slice exit criteria met</t>
+  </si>
+  <si>
+    <t>Estimates assume one developer working with Claude Code. Phase 6's buffer is reserved — do not plan work into it.</t>
+  </si>
+  <si>
+    <t>How to use this tracker</t>
+  </si>
+  <si>
+    <t>Editing</t>
+  </si>
+  <si>
+    <t>Change only the Status and Notes columns on the Tasks sheet. Everything else mirrors docs/06-project-plan.md; if the plan changes, the tracker is regenerated from it.</t>
+  </si>
+  <si>
+    <t>Status values</t>
+  </si>
+  <si>
+    <t>Default. No work begun.</t>
+  </si>
+  <si>
     <t>In progress</t>
-  </si>
-  <si>
-    <t>Implied working — repair only fires below max health, so the reactor was damaged both times. No direct log evidence yet; wave-summary line added for the next run.</t>
-  </si>
-  <si>
-    <t>DH-032</t>
-  </si>
-  <si>
-    <t>Reactor damage intake and ring targeting</t>
-  </si>
-  <si>
-    <t>Creatures reaching the ring attack it; HP falls</t>
-  </si>
-  <si>
-    <t>FR-11</t>
-  </si>
-  <si>
-    <t>Same: inferred from repairs firing. Added per-wave damage/peak-attacker summary and an ALARM line so the next run shows it directly.</t>
-  </si>
-  <si>
-    <t>DH-033</t>
-  </si>
-  <si>
-    <t>Repair interaction</t>
-  </si>
-  <si>
-    <t>Hold-interact; costs Credits; rate from Config</t>
-  </si>
-  <si>
-    <t>FR-12</t>
-  </si>
-  <si>
-    <t>User log 21:02:40 and 21:03:54: 'Shayankhankhan7 repaired +500 (5000/5000) for 40 credits', twice. Prompt, hold, credit cost and cooldown all work; credits were earned from kills.</t>
-  </si>
-  <si>
-    <t>DH-034</t>
-  </si>
-  <si>
-    <t>Defeat on reactor at 0 HP</t>
-  </si>
-  <si>
-    <t>Defeat screen; checkpoint rewards retained</t>
-  </si>
-  <si>
-    <t>Reactor at 0 calls WaveService:Defeat('reactor destroyed'). Verified path exists; /lose already proved the Defeat flow.</t>
-  </si>
-  <si>
-    <t>DH-035</t>
-  </si>
-  <si>
-    <t>Economy</t>
-  </si>
-  <si>
-    <t>Amber drops, server-owned</t>
-  </si>
-  <si>
-    <t>Amber never enters a backpack</t>
-  </si>
-  <si>
-    <t>FR-13</t>
-  </si>
-  <si>
-    <t>Proven by the level-up: Amber only accrues from CreatureDied drops, so reaching 255 means drops and crediting both work.</t>
-  </si>
-  <si>
-    <t>DH-036</t>
-  </si>
-  <si>
-    <t>Amber magnet flight and gauge</t>
-  </si>
-  <si>
-    <t>0.5-1.2s curve; value added exactly once; VFX culled on low-end</t>
-  </si>
-  <si>
-    <t>FR-14</t>
-  </si>
-  <si>
-    <t>Shards credited on arrival — the 255 total at threshold 250 shows values landing individually rather than in a lump.</t>
-  </si>
-  <si>
-    <t>DH-037</t>
-  </si>
-  <si>
-    <t>Reactor levels 1-5</t>
-  </si>
-  <si>
-    <t>Level-up fires once per threshold</t>
-  </si>
-  <si>
-    <t>FR-15</t>
-  </si>
-  <si>
-    <t>User log 21:03:43: 'REACTOR LEVEL 2 — 255 Amber (threshold 250)', ~97s in, which is the wave 4-5 window predicted from the roster sums.</t>
-  </si>
-  <si>
-    <t>DH-038</t>
-  </si>
-  <si>
-    <t>Party-scaled Amber thresholds</t>
-  </si>
-  <si>
-    <t>Solo and 6-player reach L2 at a comparable wave. Fixes a GDD defect.</t>
-  </si>
-  <si>
-    <t>FR-16</t>
-  </si>
-  <si>
-    <t>Verified by computation: Game.amberThreshold scales with party size. Solo 250/600/1050/1600 -&gt; six-player 563/1350/2363/3600 (x2.25, matching the spawn-budget income multiplier). Fixes the GDD's flat thresholds (01-gdd-review section 3).</t>
-  </si>
-  <si>
-    <t>DH-039</t>
-  </si>
-  <si>
-    <t>Fusion HUD: reactor HP</t>
-  </si>
-  <si>
-    <t>Reads clearly at a glance; low-HP state distinct</t>
-  </si>
-  <si>
-    <t>Fusion HUD reactor bar, sprung fill, turns alarm-red below 35%. Reactor column and light redden in world to match.</t>
-  </si>
-  <si>
-    <t>DH-040</t>
-  </si>
-  <si>
-    <t>Fusion HUD: Amber gauge</t>
-  </si>
-  <si>
-    <t>Shows current level and progress to next</t>
-  </si>
-  <si>
-    <t>Amber gauge fills toward the NEXT threshold rather than from zero, so it still moves between levels 4 and 5. Shows level, current/next, and credits.</t>
-  </si>
-  <si>
-    <t>DH-041</t>
-  </si>
-  <si>
-    <t>Fusion HUD: wave counter and enemies remaining</t>
-  </si>
-  <si>
-    <t>Top-centre per the GDD HUD spec</t>
-  </si>
-  <si>
-    <t>Wave counter, remaining, intermission countdown, VICTORY/DEFEAT. Moved out of Bootstrap into Client.UI.Hud with a Theme module.</t>
-  </si>
-  <si>
-    <t>DH-042</t>
-  </si>
-  <si>
-    <t>Boss</t>
-  </si>
-  <si>
-    <t>BossService: phase state machine</t>
-  </si>
-  <si>
-    <t>Phases advance on HP thresholds; recovers from a lost target</t>
-  </si>
-  <si>
-    <t>FR-20</t>
-  </si>
-  <si>
-    <t>DH-043</t>
-  </si>
-  <si>
-    <t>Telegraph system and ground indicators</t>
-  </si>
-  <si>
-    <t>Readable at the lowest graphics setting</t>
-  </si>
-  <si>
-    <t>FR-22 NFR-U5</t>
-  </si>
-  <si>
-    <t>DH-044</t>
-  </si>
-  <si>
-    <t>Invulnerability cap</t>
-  </si>
-  <si>
-    <t>No boss invulnerable more than 8 consecutive seconds; instrumented</t>
-  </si>
-  <si>
-    <t>FR-21</t>
-  </si>
-  <si>
-    <t>DH-045</t>
-  </si>
-  <si>
-    <t>Fusion boss health bar</t>
-  </si>
-  <si>
-    <t>Phase markers visible</t>
-  </si>
-  <si>
-    <t>DH-046</t>
-  </si>
-  <si>
-    <t>Boss 1: Alpha Raptor Matriarch</t>
-  </si>
-  <si>
-    <t>Summons, hunter mark, wall-leap, flank window after a missed pounce</t>
-  </si>
-  <si>
-    <t>FR-25</t>
-  </si>
-  <si>
-    <t>DH-047</t>
-  </si>
-  <si>
-    <t>Checkpoint reward and phase respawn</t>
-  </si>
-  <si>
-    <t>Exactly one reward; downed players respawn once at a transition</t>
-  </si>
-  <si>
-    <t>FR-23 FR-24</t>
-  </si>
-  <si>
-    <t>DH-048</t>
-  </si>
-  <si>
-    <t>Exploration</t>
-  </si>
-  <si>
-    <t>ExplorationService: wave pause</t>
-  </si>
-  <si>
-    <t>No spawns, no reactor damage during exploration</t>
-  </si>
-  <si>
-    <t>FR-32</t>
-  </si>
-  <si>
-    <t>DH-049</t>
-  </si>
-  <si>
-    <t>150s timer with 30s and 10s warnings</t>
-  </si>
-  <si>
-    <t>Warnings fire once each</t>
-  </si>
-  <si>
-    <t>FR-33</t>
-  </si>
-  <si>
-    <t>DH-050</t>
-  </si>
-  <si>
-    <t>Safe recall at zero</t>
-  </si>
-  <si>
-    <t>Distant players recalled, not killed. No fall damage.</t>
-  </si>
-  <si>
-    <t>FR-34</t>
-  </si>
-  <si>
-    <t>DH-051</t>
-  </si>
-  <si>
-    <t>Sector 1 gating on boss AND Amber level</t>
-  </si>
-  <si>
-    <t>Neither condition alone opens it</t>
-  </si>
-  <si>
-    <t>DH-052</t>
-  </si>
-  <si>
-    <t>Late gauge fill case</t>
-  </si>
-  <si>
-    <t>If the gauge fills mid-wave, the sector opens then. Defines what the GDD leaves open.</t>
-  </si>
-  <si>
-    <t>FR-31</t>
-  </si>
-  <si>
-    <t>DH-053</t>
-  </si>
-  <si>
-    <t>Survivor</t>
-  </si>
-  <si>
-    <t>SurvivorService: escort NPC and waypoints</t>
-  </si>
-  <si>
-    <t>Authored waypoints, not dynamic pathfinding</t>
-  </si>
-  <si>
-    <t>FR-40</t>
-  </si>
-  <si>
-    <t>DH-054</t>
-  </si>
-  <si>
-    <t>Stuck recovery</t>
-  </si>
-  <si>
-    <t>Relocates to the last safe waypoint after 8s</t>
-  </si>
-  <si>
-    <t>FR-41</t>
-  </si>
-  <si>
-    <t>DH-055</t>
-  </si>
-  <si>
-    <t>Safe room arrival and team credit</t>
-  </si>
-  <si>
-    <t>Credit shared team-wide; survivor visibly present</t>
-  </si>
-  <si>
-    <t>DH-056</t>
-  </si>
-  <si>
-    <t>Hatchery</t>
-  </si>
-  <si>
-    <t>Nest and guardian</t>
-  </si>
-  <si>
-    <t>Kill OR distract both yield the egg</t>
-  </si>
-  <si>
-    <t>FR-42</t>
-  </si>
-  <si>
-    <t>DH-057</t>
-  </si>
-  <si>
-    <t>Egg carry state</t>
-  </si>
-  <si>
-    <t>Occupies an objective slot, slows sprint, icon above carrier</t>
-  </si>
-  <si>
-    <t>FR-43</t>
-  </si>
-  <si>
-    <t>DH-058</t>
-  </si>
-  <si>
-    <t>Hatchery deposit secures the egg</t>
-  </si>
-  <si>
-    <t>Survives a forced run loss</t>
-  </si>
-  <si>
-    <t>FR-44</t>
-  </si>
-  <si>
-    <t>DH-059</t>
-  </si>
-  <si>
-    <t>Incubation on server timestamps</t>
-  </si>
-  <si>
-    <t>Survives reconnect. Timestamp-based, never tick-based.</t>
-  </si>
-  <si>
-    <t>FR-45 NFR-D4</t>
-  </si>
-  <si>
-    <t>DH-060</t>
-  </si>
-  <si>
-    <t>Idempotent pet grant</t>
-  </si>
-  <si>
-    <t>Exactly one pet. Duplicate grant IDs rejected. HIGHEST data-integrity risk.</t>
-  </si>
-  <si>
-    <t>FR-46 NFR-D3</t>
-  </si>
-  <si>
-    <t>DH-061</t>
-  </si>
-  <si>
-    <t>Collection</t>
-  </si>
-  <si>
-    <t>Dino Codex (minimal)</t>
-  </si>
-  <si>
-    <t>Seen / defeated / egg / hatched per species; persists</t>
-  </si>
-  <si>
-    <t>S</t>
-  </si>
-  <si>
-    <t>FR-47</t>
-  </si>
-  <si>
-    <t>DH-062</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>DataService profile keys</t>
-  </si>
-  <si>
-    <t>DinoCodex, EggInventory, PetInventory, SurvivorLog; schema versioned</t>
-  </si>
-  <si>
-    <t>NFR-D5</t>
-  </si>
-  <si>
-    <t>DH-063</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>Three classes with passives</t>
-  </si>
-  <si>
-    <t>Ranger, Engineer, Medic. Duplicates allowed.</t>
-  </si>
-  <si>
-    <t>FR-50</t>
-  </si>
-  <si>
-    <t>DH-064</t>
-  </si>
-  <si>
-    <t>Class abilities on 60s cooldown</t>
-  </si>
-  <si>
-    <t>Scan Pulse, Shock Fence, Healing Mist</t>
-  </si>
-  <si>
-    <t>DH-065</t>
-  </si>
-  <si>
-    <t>Downed state (25s)</t>
-  </si>
-  <si>
-    <t>Not instant death</t>
-  </si>
-  <si>
-    <t>FR-51</t>
-  </si>
-  <si>
-    <t>DH-066</t>
-  </si>
-  <si>
-    <t>Revive (3s, interrupted by damage)</t>
-  </si>
-  <si>
-    <t>Verified in multiplayer</t>
-  </si>
-  <si>
-    <t>FR-52</t>
-  </si>
-  <si>
-    <t>DH-067</t>
-  </si>
-  <si>
-    <t>Next-wave respawn and credit penalty</t>
-  </si>
-  <si>
-    <t>Solo case explicitly defined. Fixes a GDD contradiction.</t>
-  </si>
-  <si>
-    <t>FR-53</t>
-  </si>
-  <si>
-    <t>DH-068</t>
-  </si>
-  <si>
-    <t>Run perks: milestone 3-choice draft</t>
-  </si>
-  <si>
-    <t>Six perks; stacks respected</t>
-  </si>
-  <si>
-    <t>FR-06</t>
-  </si>
-  <si>
-    <t>DH-069</t>
-  </si>
-  <si>
-    <t>Hardening</t>
-  </si>
-  <si>
-    <t>Performance pass</t>
-  </si>
-  <si>
-    <t>50+ FPS on reference mobile at wave 20; memory flat across a run</t>
-  </si>
-  <si>
-    <t>NFR-P1 NFR-P4</t>
-  </si>
-  <si>
-    <t>DH-070</t>
-  </si>
-  <si>
-    <t>Mobile device test</t>
-  </si>
-  <si>
-    <t>Touch reaches every action; UI never blocks controls</t>
-  </si>
-  <si>
-    <t>NFR-C2 NFR-C4</t>
-  </si>
-  <si>
-    <t>DH-071</t>
-  </si>
-  <si>
-    <t>Exploit pass</t>
-  </si>
-  <si>
-    <t>Forged hits, forged rewards, duplicate egg grants all rejected</t>
-  </si>
-  <si>
-    <t>NFR-S1 NFR-S5</t>
-  </si>
-  <si>
-    <t>DH-072</t>
-  </si>
-  <si>
-    <t>Bug fix and stabilisation buffer</t>
-  </si>
-  <si>
-    <t>Reserved. Do not plan work into it.</t>
-  </si>
-  <si>
-    <t>DH-073</t>
-  </si>
-  <si>
-    <t>Export the script tree to the repo</t>
-  </si>
-  <si>
-    <t>export_rbxm of the code tree committed to git — the only version control the code has</t>
-  </si>
-  <si>
-    <t>Added 2026-09-28: no Rojo means no automatic git coverage.</t>
-  </si>
-  <si>
-    <t>Snapshot committed with a README covering restore steps and the binary-diff limitation.</t>
-  </si>
-  <si>
-    <t>DH-074</t>
-  </si>
-  <si>
-    <t>Write Maid/Signal/ServiceBag unit checks</t>
-  </si>
-  <si>
-    <t>Each exercised in a playtest: cleanup runs, signal fires, two-phase init order holds</t>
-  </si>
-  <si>
-    <t>Added 2026-09-28: hand-written replacements for Nevermore need proving.</t>
-  </si>
-  <si>
-    <t>ServiceBag: 4 services Init/Start clean. Maid: parse bug found and fixed (call on a function-type cast). Signal: CreatureDied/ReachedReactor delivered to _DevSpawner.</t>
-  </si>
-  <si>
-    <t>74 tasks</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Phase rollup</t>
-  </si>
-  <si>
-    <t>Every figure here is a formula over the Tasks sheet. Nothing to edit.</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Goal</t>
-  </si>
-  <si>
-    <t>Tasks</t>
-  </si>
-  <si>
-    <t>Done (d)</t>
-  </si>
-  <si>
-    <t>% complete</t>
-  </si>
-  <si>
-    <t>Exit criteria</t>
-  </si>
-  <si>
-    <t>Nothing else can start until this is done</t>
-  </si>
-  <si>
-    <t>A trivial Fusion HUD element renders in-game from a file edit</t>
-  </si>
-  <si>
-    <t>Blockout and creature stub</t>
-  </si>
-  <si>
-    <t>Prove one creature, one gun, one lane</t>
-  </si>
-  <si>
-    <t>A creature walks a lane and dies to one rifle shot</t>
-  </si>
-  <si>
-    <t>The wave loop</t>
-  </si>
-  <si>
-    <t>Twenty finite waves with four creature roles</t>
-  </si>
-  <si>
-    <t>A full 20-wave run completes</t>
-  </si>
-  <si>
-    <t>The spine</t>
-  </si>
-  <si>
-    <t>Something to defend; the run can be won or lost</t>
-  </si>
-  <si>
-    <t>A run can be won and lost; the reactor is the objective</t>
-  </si>
-  <si>
-    <t>Boss and exploration</t>
-  </si>
-  <si>
-    <t>The loop the game is actually about</t>
-  </si>
-  <si>
-    <t>Wave 4 boss to sector opens to exploration to safe return</t>
-  </si>
-  <si>
-    <t>The collection loop</t>
-  </si>
-  <si>
-    <t>The reason players come back</t>
-  </si>
-  <si>
-    <t>An egg survives a disconnect and hatches into exactly one pet</t>
-  </si>
-  <si>
-    <t>Players and hardening</t>
-  </si>
-  <si>
-    <t>Make it hold up</t>
-  </si>
-  <si>
-    <t>MVP slice exit criteria met</t>
-  </si>
-  <si>
-    <t>Estimates assume one developer working with Claude Code. Phase 6's buffer is reserved — do not plan work into it.</t>
-  </si>
-  <si>
-    <t>How to use this tracker</t>
-  </si>
-  <si>
-    <t>Editing</t>
-  </si>
-  <si>
-    <t>Change only the Status and Notes columns on the Tasks sheet. Everything else mirrors docs/06-project-plan.md; if the plan changes, the tracker is regenerated from it.</t>
-  </si>
-  <si>
-    <t>Status values</t>
-  </si>
-  <si>
-    <t>Default. No work begun.</t>
   </si>
   <si>
     <t>Actively being worked.</t>
@@ -2930,7 +2930,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:11" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
         <v>157</v>
       </c>
@@ -2956,18 +2956,18 @@
         <v>18</v>
       </c>
       <c r="I36" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="J36" s="9" t="s">
         <v>61</v>
       </c>
       <c r="K36" s="8" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="16" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
-        <v>163</v>
       </c>
       <c r="B37" s="17">
         <v>3</v>
@@ -2976,10 +2976,10 @@
         <v>158</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E37" s="8" t="s">
         <v>164</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>165</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>157</v>
@@ -2991,18 +2991,18 @@
         <v>18</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="J37" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="K37" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="K37" s="8" t="s">
+    </row>
+    <row r="38" spans="1:11" ht="76.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
         <v>167</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
-        <v>168</v>
       </c>
       <c r="B38" s="17">
         <v>3</v>
@@ -3011,13 +3011,13 @@
         <v>158</v>
       </c>
       <c r="D38" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E38" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="8" t="s">
-        <v>170</v>
-      </c>
       <c r="F38" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G38" s="10">
         <v>0.5</v>
@@ -3029,15 +3029,15 @@
         <v>38</v>
       </c>
       <c r="J38" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="K38" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="K38" s="8" t="s">
+    </row>
+    <row r="39" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="16" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
-        <v>173</v>
       </c>
       <c r="B39" s="17">
         <v>3</v>
@@ -3046,13 +3046,13 @@
         <v>158</v>
       </c>
       <c r="D39" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E39" s="8" t="s">
-        <v>175</v>
-      </c>
       <c r="F39" s="9" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G39" s="10">
         <v>0.4</v>
@@ -3061,30 +3061,30 @@
         <v>18</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>155</v>
       </c>
       <c r="K39" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="16" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
-        <v>177</v>
       </c>
       <c r="B40" s="17">
         <v>3</v>
       </c>
       <c r="C40" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="D40" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="D40" s="7" t="s">
+      <c r="E40" s="8" t="s">
         <v>179</v>
-      </c>
-      <c r="E40" s="8" t="s">
-        <v>180</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>157</v>
@@ -3099,30 +3099,30 @@
         <v>38</v>
       </c>
       <c r="J40" s="9" t="s">
+        <v>180</v>
+      </c>
+      <c r="K40" s="8" t="s">
         <v>181</v>
-      </c>
-      <c r="K40" s="8" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B41" s="17">
         <v>3</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D41" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E41" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="E41" s="8" t="s">
-        <v>185</v>
-      </c>
       <c r="F41" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G41" s="10">
         <v>0.75</v>
@@ -3134,30 +3134,30 @@
         <v>38</v>
       </c>
       <c r="J41" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="K41" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="K41" s="8" t="s">
+    </row>
+    <row r="42" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="16" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
-        <v>188</v>
       </c>
       <c r="B42" s="17">
         <v>3</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D42" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="E42" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="F42" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="G42" s="10">
         <v>0.5</v>
@@ -3169,30 +3169,30 @@
         <v>38</v>
       </c>
       <c r="J42" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="K42" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="K42" s="8" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="43" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="16" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B43" s="17">
         <v>3</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D43" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E43" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="E43" s="8" t="s">
-        <v>195</v>
-      </c>
       <c r="F43" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G43" s="10">
         <v>0.5</v>
@@ -3204,15 +3204,15 @@
         <v>38</v>
       </c>
       <c r="J43" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="K43" s="8" t="s">
         <v>196</v>
       </c>
-      <c r="K43" s="8" t="s">
+    </row>
+    <row r="44" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="16" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" ht="51" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>198</v>
       </c>
       <c r="B44" s="17">
         <v>3</v>
@@ -3221,10 +3221,10 @@
         <v>49</v>
       </c>
       <c r="D44" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>200</v>
       </c>
       <c r="F44" s="9" t="s">
         <v>157</v>
@@ -3236,16 +3236,16 @@
         <v>18</v>
       </c>
       <c r="I44" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="J44" s="9"/>
       <c r="K44" s="8" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="16" t="s">
         <v>201</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" ht="63.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
-        <v>202</v>
       </c>
       <c r="B45" s="17">
         <v>3</v>
@@ -3254,13 +3254,13 @@
         <v>49</v>
       </c>
       <c r="D45" s="7" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="E45" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="F45" s="9" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G45" s="10">
         <v>0.5</v>
@@ -3269,16 +3269,16 @@
         <v>18</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="J45" s="9"/>
       <c r="K45" s="8" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B46" s="17">
         <v>3</v>
@@ -3287,10 +3287,10 @@
         <v>49</v>
       </c>
       <c r="D46" s="7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="E46" s="8" t="s">
-        <v>208</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>112</v>
@@ -3302,28 +3302,28 @@
         <v>18</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>161</v>
+        <v>38</v>
       </c>
       <c r="J46" s="9"/>
       <c r="K46" s="8" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B47" s="19">
         <v>4</v>
       </c>
       <c r="C47" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="D47" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D47" s="7" t="s">
+      <c r="E47" s="8" t="s">
         <v>212</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>213</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>112</v>
@@ -3338,28 +3338,28 @@
         <v>32</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K47" s="8"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B48" s="19">
         <v>4</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D48" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="E48" s="8" t="s">
-        <v>217</v>
-      </c>
       <c r="F48" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G48" s="10">
         <v>0.75</v>
@@ -3371,28 +3371,28 @@
         <v>32</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K48" s="8"/>
     </row>
     <row r="49" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B49" s="19">
         <v>4</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D49" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="E49" s="8" t="s">
         <v>220</v>
       </c>
-      <c r="E49" s="8" t="s">
-        <v>221</v>
-      </c>
       <c r="F49" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G49" s="10">
         <v>0.25</v>
@@ -3404,28 +3404,28 @@
         <v>32</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K49" s="8"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B50" s="19">
         <v>4</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D50" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E50" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E50" s="8" t="s">
-        <v>225</v>
-      </c>
       <c r="F50" s="9" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G50" s="10">
         <v>0.4</v>
@@ -3441,22 +3441,22 @@
     </row>
     <row r="51" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B51" s="19">
         <v>4</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D51" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" s="8" t="s">
         <v>227</v>
       </c>
-      <c r="E51" s="8" t="s">
-        <v>228</v>
-      </c>
       <c r="F51" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G51" s="10">
         <v>1.25</v>
@@ -3468,28 +3468,28 @@
         <v>32</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="K51" s="8"/>
     </row>
     <row r="52" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B52" s="19">
         <v>4</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D52" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E52" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="E52" s="8" t="s">
-        <v>232</v>
-      </c>
       <c r="F52" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G52" s="10">
         <v>0.5</v>
@@ -3501,28 +3501,28 @@
         <v>32</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="K52" s="8"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B53" s="19">
         <v>4</v>
       </c>
       <c r="C53" s="18" t="s">
+        <v>234</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="E53" s="8" t="s">
         <v>236</v>
       </c>
-      <c r="E53" s="8" t="s">
-        <v>237</v>
-      </c>
       <c r="F53" s="9" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G53" s="10">
         <v>0.5</v>
@@ -3534,28 +3534,28 @@
         <v>32</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B54" s="19">
         <v>4</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D54" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="E54" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="E54" s="8" t="s">
-        <v>241</v>
-      </c>
       <c r="F54" s="9" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G54" s="10">
         <v>0.4</v>
@@ -3567,28 +3567,28 @@
         <v>32</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B55" s="19">
         <v>4</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D55" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="E55" s="8" t="s">
-        <v>245</v>
-      </c>
       <c r="F55" s="9" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G55" s="10">
         <v>0.5</v>
@@ -3600,28 +3600,28 @@
         <v>32</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B56" s="19">
         <v>4</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D56" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E56" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E56" s="8" t="s">
-        <v>249</v>
-      </c>
       <c r="F56" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G56" s="10">
         <v>0.5</v>
@@ -3639,22 +3639,22 @@
     </row>
     <row r="57" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B57" s="19">
         <v>4</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D57" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="E57" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="E57" s="8" t="s">
-        <v>252</v>
-      </c>
       <c r="F57" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G57" s="10">
         <v>0.5</v>
@@ -3666,28 +3666,28 @@
         <v>32</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="K57" s="8"/>
     </row>
     <row r="58" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B58" s="21">
         <v>5</v>
       </c>
       <c r="C58" s="20" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="D58" s="7" t="s">
+      <c r="E58" s="8" t="s">
         <v>256</v>
       </c>
-      <c r="E58" s="8" t="s">
-        <v>257</v>
-      </c>
       <c r="F58" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G58" s="10">
         <v>1</v>
@@ -3699,28 +3699,28 @@
         <v>32</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K58" s="8"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B59" s="21">
         <v>5</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E59" s="8" t="s">
         <v>260</v>
       </c>
-      <c r="E59" s="8" t="s">
-        <v>261</v>
-      </c>
       <c r="F59" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G59" s="10">
         <v>0.4</v>
@@ -3732,28 +3732,28 @@
         <v>32</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="K59" s="8"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B60" s="21">
         <v>5</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D60" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="E60" s="8" t="s">
-        <v>265</v>
-      </c>
       <c r="F60" s="9" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G60" s="10">
         <v>0.4</v>
@@ -3765,28 +3765,28 @@
         <v>32</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="K60" s="8"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B61" s="21">
         <v>5</v>
       </c>
       <c r="C61" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D61" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="D61" s="7" t="s">
+      <c r="E61" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="E61" s="8" t="s">
-        <v>269</v>
-      </c>
       <c r="F61" s="9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G61" s="10">
         <v>0.75</v>
@@ -3798,28 +3798,28 @@
         <v>32</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="K61" s="8"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B62" s="21">
         <v>5</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D62" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="E62" s="8" t="s">
         <v>272</v>
       </c>
-      <c r="E62" s="8" t="s">
-        <v>273</v>
-      </c>
       <c r="F62" s="9" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G62" s="10">
         <v>0.5</v>
@@ -3831,28 +3831,28 @@
         <v>32</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B63" s="21">
         <v>5</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D63" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="E63" s="8" t="s">
         <v>276</v>
       </c>
-      <c r="E63" s="8" t="s">
-        <v>277</v>
-      </c>
       <c r="F63" s="9" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G63" s="10">
         <v>0.5</v>
@@ -3864,28 +3864,28 @@
         <v>32</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="K63" s="8"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B64" s="21">
         <v>5</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D64" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E64" s="8" t="s">
         <v>280</v>
       </c>
-      <c r="E64" s="8" t="s">
-        <v>281</v>
-      </c>
       <c r="F64" s="9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G64" s="10">
         <v>0.75</v>
@@ -3897,28 +3897,28 @@
         <v>32</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="K64" s="8"/>
     </row>
     <row r="65" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B65" s="21">
         <v>5</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D65" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E65" s="8" t="s">
         <v>284</v>
       </c>
-      <c r="E65" s="8" t="s">
-        <v>285</v>
-      </c>
       <c r="F65" s="9" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G65" s="10">
         <v>0.75</v>
@@ -3930,61 +3930,61 @@
         <v>32</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="K65" s="8"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B66" s="21">
         <v>5</v>
       </c>
       <c r="C66" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D66" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="D66" s="7" t="s">
+      <c r="E66" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="E66" s="8" t="s">
-        <v>290</v>
-      </c>
       <c r="F66" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G66" s="10">
         <v>0.75</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="K66" s="8"/>
     </row>
     <row r="67" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B67" s="21">
         <v>5</v>
       </c>
       <c r="C67" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D67" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="D67" s="7" t="s">
+      <c r="E67" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="E67" s="8" t="s">
-        <v>296</v>
-      </c>
       <c r="F67" s="9" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G67" s="10">
         <v>0.5</v>
@@ -3996,25 +3996,25 @@
         <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K67" s="8"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B68" s="23">
         <v>6</v>
       </c>
       <c r="C68" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="D68" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="D68" s="7" t="s">
+      <c r="E68" s="8" t="s">
         <v>300</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>301</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>112</v>
@@ -4029,28 +4029,28 @@
         <v>32</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K68" s="8"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B69" s="23">
         <v>6</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D69" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="E69" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="E69" s="8" t="s">
-        <v>305</v>
-      </c>
       <c r="F69" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="G69" s="10">
         <v>0.75</v>
@@ -4062,25 +4062,25 @@
         <v>32</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K69" s="8"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B70" s="23">
         <v>6</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D70" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>307</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>308</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>107</v>
@@ -4095,28 +4095,28 @@
         <v>32</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="K70" s="8"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B71" s="23">
         <v>6</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D71" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="E71" s="8" t="s">
         <v>311</v>
       </c>
-      <c r="E71" s="8" t="s">
-        <v>312</v>
-      </c>
       <c r="F71" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G71" s="10">
         <v>0.4</v>
@@ -4128,28 +4128,28 @@
         <v>32</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="K71" s="8"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B72" s="23">
         <v>6</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D72" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="E72" s="8" t="s">
         <v>315</v>
       </c>
-      <c r="E72" s="8" t="s">
-        <v>316</v>
-      </c>
       <c r="F72" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="G72" s="10">
         <v>0.4</v>
@@ -4161,25 +4161,25 @@
         <v>32</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B73" s="23">
         <v>6</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D73" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E73" s="8" t="s">
         <v>319</v>
-      </c>
-      <c r="E73" s="8" t="s">
-        <v>320</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>112</v>
@@ -4188,34 +4188,34 @@
         <v>0.6</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="K73" s="8"/>
     </row>
     <row r="74" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B74" s="23">
         <v>6</v>
       </c>
       <c r="C74" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="D74" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="D74" s="7" t="s">
+      <c r="E74" s="8" t="s">
         <v>324</v>
       </c>
-      <c r="E74" s="8" t="s">
-        <v>325</v>
-      </c>
       <c r="F74" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G74" s="10">
         <v>0.75</v>
@@ -4227,28 +4227,28 @@
         <v>32</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="K74" s="8"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B75" s="23">
         <v>6</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D75" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="E75" s="8" t="s">
         <v>328</v>
       </c>
-      <c r="E75" s="8" t="s">
-        <v>329</v>
-      </c>
       <c r="F75" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="G75" s="10">
         <v>0.5</v>
@@ -4260,28 +4260,28 @@
         <v>32</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="K75" s="8"/>
     </row>
     <row r="76" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B76" s="23">
         <v>6</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D76" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="E76" s="8" t="s">
         <v>332</v>
       </c>
-      <c r="E76" s="8" t="s">
-        <v>333</v>
-      </c>
       <c r="F76" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G76" s="10">
         <v>0.75</v>
@@ -4293,28 +4293,28 @@
         <v>32</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K76" s="8"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B77" s="23">
         <v>6</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D77" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="E77" s="8" t="s">
         <v>336</v>
       </c>
-      <c r="E77" s="8" t="s">
-        <v>337</v>
-      </c>
       <c r="F77" s="9" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -4330,7 +4330,7 @@
     </row>
     <row r="78" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B78" s="23">
         <v>0</v>
@@ -4339,10 +4339,10 @@
         <v>54</v>
       </c>
       <c r="D78" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="E78" s="8" t="s">
         <v>339</v>
-      </c>
-      <c r="E78" s="8" t="s">
-        <v>340</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>48</v>
@@ -4357,15 +4357,15 @@
         <v>38</v>
       </c>
       <c r="J78" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="K78" t="s">
         <v>341</v>
-      </c>
-      <c r="K78" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B79" s="23">
         <v>0</v>
@@ -4374,10 +4374,10 @@
         <v>54</v>
       </c>
       <c r="D79" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="E79" s="8" t="s">
         <v>344</v>
-      </c>
-      <c r="E79" s="8" t="s">
-        <v>345</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>40</v>
@@ -4386,24 +4386,24 @@
         <v>0.5</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>38</v>
       </c>
       <c r="J79" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="K79" t="s">
         <v>346</v>
-      </c>
-      <c r="K79" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="D80" s="24" t="s">
+        <v>347</v>
+      </c>
+      <c r="F80" s="24" t="s">
         <v>348</v>
-      </c>
-      <c r="F80" s="24" t="s">
-        <v>349</v>
       </c>
       <c r="G80" s="25">
         <f>SUM(G6:G79)</f>
@@ -4455,12 +4455,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4468,13 +4468,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>354</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>38</v>
@@ -4483,13 +4483,13 @@
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="I4" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4500,7 +4500,7 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D5" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A5)</f>
@@ -4523,7 +4523,7 @@
         <v>0.53333333333333333</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4531,10 +4531,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="29" t="s">
+        <v>359</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>360</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>361</v>
       </c>
       <c r="D6" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A6)</f>
@@ -4557,7 +4557,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4565,10 +4565,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>363</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>364</v>
       </c>
       <c r="D7" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A7)</f>
@@ -4591,7 +4591,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4599,10 +4599,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>366</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>367</v>
       </c>
       <c r="D8" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A8)</f>
@@ -4610,7 +4610,7 @@
       </c>
       <c r="E8" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A8,Tasks!$I$6:$I$79,"Done")</f>
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F8" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A8)</f>
@@ -4618,14 +4618,14 @@
       </c>
       <c r="G8" s="10">
         <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A8,Tasks!$I$6:$I$79,"Done")</f>
-        <v>2.75</v>
+        <v>5.7000000000000011</v>
       </c>
       <c r="H8" s="28">
         <f t="shared" si="0"/>
-        <v>0.48245614035087708</v>
+        <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4633,10 +4633,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="32" t="s">
+        <v>368</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>369</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>370</v>
       </c>
       <c r="D9" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A9)</f>
@@ -4659,7 +4659,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4667,10 +4667,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>373</v>
       </c>
       <c r="D10" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A10)</f>
@@ -4693,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4701,10 +4701,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
+        <v>374</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>375</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>376</v>
       </c>
       <c r="D11" s="27">
         <f>COUNTIFS(Tasks!$B$6:$B$79,$A11)</f>
@@ -4727,13 +4727,13 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="36">
@@ -4742,7 +4742,7 @@
       </c>
       <c r="E12" s="36">
         <f>SUM(E5:E11)</f>
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F12" s="37">
         <f>SUM(F5:F11)</f>
@@ -4750,17 +4750,17 @@
       </c>
       <c r="G12" s="37">
         <f>SUM(G5:G11)</f>
-        <v>16.05</v>
+        <v>19</v>
       </c>
       <c r="H12" s="38">
         <f t="shared" si="0"/>
-        <v>0.40225563909774437</v>
+        <v>0.47619047619047622</v>
       </c>
       <c r="I12" s="35"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="39" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
   </sheetData>
@@ -4779,7 +4779,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4788,10 +4788,10 @@
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="B4" s="40" t="s">
         <v>380</v>
-      </c>
-      <c r="B4" s="40" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4800,7 +4800,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B6" s="40"/>
     </row>
@@ -4809,12 +4809,12 @@
         <v>32</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>161</v>
+        <v>383</v>
       </c>
       <c r="B8" s="40" t="s">
         <v>384</v>
@@ -4864,7 +4864,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B15" s="40" t="s">
         <v>391</v>

--- a/Dino-Hunt-Tasks.xlsx
+++ b/Dino-Hunt-Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game Development\Roblox\Games\Deno-Hunt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD710EF0-B309-4240-87A1-B1A863D3D7E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6997323-A86D-4A0F-A850-5B61A82A5B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="412">
   <si>
     <t>Dino Hunt — implementation task tracker</t>
   </si>
@@ -679,9 +679,15 @@
     <t>Phases advance on HP thresholds; recovers from a lost target</t>
   </si>
   <si>
+    <t>In progress</t>
+  </si>
+  <si>
     <t>FR-20</t>
   </si>
   <si>
+    <t>BossService: phase machine driven by health fraction, watched on Heartbeat. 3 phases for Boss 1. Awaiting playtest.</t>
+  </si>
+  <si>
     <t>DH-043</t>
   </si>
   <si>
@@ -694,6 +700,9 @@
     <t>FR-22 NFR-U5</t>
   </si>
   <si>
+    <t>Shared.Util.Telegraph: flat Neon circle filling from the centre over the warning time, readable at lowest graphics (NFR-U5). Server-created so every client can trust it.</t>
+  </si>
+  <si>
     <t>DH-044</t>
   </si>
   <si>
@@ -706,6 +715,9 @@
     <t>FR-21</t>
   </si>
   <si>
+    <t>Clamped in code, not trusted to the table: a phase asking for &gt;8s is clamped and warned. Longest invulnerability printed at boss death. Verified statically: all 3 phases under cap.</t>
+  </si>
+  <si>
     <t>DH-045</t>
   </si>
   <si>
@@ -715,6 +727,9 @@
     <t>Phase markers visible</t>
   </si>
   <si>
+    <t>Fusion boss panel under the wave panel, Visible bound to BossMaxHealth&gt;0, shows name, phase N/M and percentage.</t>
+  </si>
+  <si>
     <t>DH-046</t>
   </si>
   <si>
@@ -727,6 +742,9 @@
     <t>FR-25</t>
   </si>
   <si>
+    <t>Alpha Raptor Matriarch: 12000 HP solo (~100s at ~120 effective dps, inside the GDD 90-150s band), 3 phases, telegraphed pounce, hunter mark, summons in phase 2, flank window on a missed pounce.</t>
+  </si>
+  <si>
     <t>DH-047</t>
   </si>
   <si>
@@ -739,6 +757,9 @@
     <t>FR-23 FR-24</t>
   </si>
   <si>
+    <t>Checkpoint reward granted immediately on death (250 credits, all players) so a later failure cannot erase it. Phase transitions respawn defeated players (FR-24).</t>
+  </si>
+  <si>
     <t>DH-048</t>
   </si>
   <si>
@@ -1081,7 +1102,19 @@
     <t>ServiceBag: 4 services Init/Start clean. Maid: parse bug found and fixed (call on a function-type cast). Signal: CreatureDied/ReachedReactor delivered to _DevSpawner.</t>
   </si>
   <si>
-    <t>74 tasks</t>
+    <t>DH-075</t>
+  </si>
+  <si>
+    <t>Creatures damage nearby players</t>
+  </si>
+  <si>
+    <t>A creature within AttackRange damages the nearest living player on its AttackInterval; player health falls and reaches 0</t>
+  </si>
+  <si>
+    <t>Added 2026-09-28: config carried damage/AttackInterval/AttackRange from Phase 1 but nothing used them - creatures walked past players to the reactor. Boss telegraphs are meaningless without it.</t>
+  </si>
+  <si>
+    <t>75 tasks</t>
   </si>
   <si>
     <t>TOTAL</t>
@@ -1187,9 +1220,6 @@
   </si>
   <si>
     <t>Default. No work begun.</t>
-  </si>
-  <si>
-    <t>In progress</t>
   </si>
   <si>
     <t>Actively being worked.</t>
@@ -1846,7 +1876,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -3335,16 +3365,18 @@
         <v>18</v>
       </c>
       <c r="I47" s="9" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>213</v>
-      </c>
-      <c r="K47" s="8"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>214</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" ht="76.5" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B48" s="19">
         <v>4</v>
@@ -3353,10 +3385,10 @@
         <v>210</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E48" s="8" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F48" s="9" t="s">
         <v>209</v>
@@ -3368,16 +3400,18 @@
         <v>18</v>
       </c>
       <c r="I48" s="9" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="J48" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="K48" s="8"/>
+        <v>219</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>220</v>
+      </c>
     </row>
     <row r="49" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B49" s="19">
         <v>4</v>
@@ -3386,10 +3420,10 @@
         <v>210</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>209</v>
@@ -3401,16 +3435,18 @@
         <v>18</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="K49" s="8"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" ht="51" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B50" s="19">
         <v>4</v>
@@ -3419,10 +3455,10 @@
         <v>210</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F50" s="9" t="s">
         <v>209</v>
@@ -3434,14 +3470,16 @@
         <v>18</v>
       </c>
       <c r="I50" s="9" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="J50" s="9"/>
-      <c r="K50" s="8"/>
+      <c r="K50" s="8" t="s">
+        <v>229</v>
+      </c>
     </row>
     <row r="51" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B51" s="19">
         <v>4</v>
@@ -3450,13 +3488,13 @@
         <v>210</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="F51" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="G51" s="10">
         <v>1.25</v>
@@ -3465,16 +3503,18 @@
         <v>18</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>228</v>
-      </c>
-      <c r="K51" s="8"/>
+        <v>233</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>234</v>
+      </c>
     </row>
     <row r="52" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B52" s="19">
         <v>4</v>
@@ -3483,13 +3523,13 @@
         <v>210</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F52" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G52" s="10">
         <v>0.5</v>
@@ -3498,31 +3538,33 @@
         <v>18</v>
       </c>
       <c r="I52" s="9" t="s">
-        <v>32</v>
+        <v>213</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>232</v>
-      </c>
-      <c r="K52" s="8"/>
+        <v>238</v>
+      </c>
+      <c r="K52" s="8" t="s">
+        <v>239</v>
+      </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B53" s="19">
         <v>4</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G53" s="10">
         <v>0.5</v>
@@ -3534,28 +3576,28 @@
         <v>32</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="K53" s="8"/>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B54" s="19">
         <v>4</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F54" s="9" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="G54" s="10">
         <v>0.4</v>
@@ -3567,28 +3609,28 @@
         <v>32</v>
       </c>
       <c r="J54" s="9" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="K54" s="8"/>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B55" s="19">
         <v>4</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="G55" s="10">
         <v>0.5</v>
@@ -3600,25 +3642,25 @@
         <v>32</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="K55" s="8"/>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="B56" s="19">
         <v>4</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>192</v>
@@ -3639,22 +3681,22 @@
     </row>
     <row r="57" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B57" s="19">
         <v>4</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="F57" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G57" s="10">
         <v>0.5</v>
@@ -3666,28 +3708,28 @@
         <v>32</v>
       </c>
       <c r="J57" s="9" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="K57" s="8"/>
     </row>
     <row r="58" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="20" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="B58" s="21">
         <v>5</v>
       </c>
       <c r="C58" s="20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D58" s="7" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F58" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G58" s="10">
         <v>1</v>
@@ -3699,28 +3741,28 @@
         <v>32</v>
       </c>
       <c r="J58" s="9" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="K58" s="8"/>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="20" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B59" s="21">
         <v>5</v>
       </c>
       <c r="C59" s="20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F59" s="9" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G59" s="10">
         <v>0.4</v>
@@ -3732,28 +3774,28 @@
         <v>32</v>
       </c>
       <c r="J59" s="9" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="K59" s="8"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="20" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B60" s="21">
         <v>5</v>
       </c>
       <c r="C60" s="20" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F60" s="9" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="G60" s="10">
         <v>0.4</v>
@@ -3765,28 +3807,28 @@
         <v>32</v>
       </c>
       <c r="J60" s="9" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="K60" s="8"/>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="20" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B61" s="21">
         <v>5</v>
       </c>
       <c r="C61" s="20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="F61" s="9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="G61" s="10">
         <v>0.75</v>
@@ -3798,28 +3840,28 @@
         <v>32</v>
       </c>
       <c r="J61" s="9" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="K61" s="8"/>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="20" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B62" s="21">
         <v>5</v>
       </c>
       <c r="C62" s="20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="F62" s="9" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="G62" s="10">
         <v>0.5</v>
@@ -3831,28 +3873,28 @@
         <v>32</v>
       </c>
       <c r="J62" s="9" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="K62" s="8"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="20" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="B63" s="21">
         <v>5</v>
       </c>
       <c r="C63" s="20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="F63" s="9" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="G63" s="10">
         <v>0.5</v>
@@ -3864,28 +3906,28 @@
         <v>32</v>
       </c>
       <c r="J63" s="9" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="K63" s="8"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="20" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B64" s="21">
         <v>5</v>
       </c>
       <c r="C64" s="20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="F64" s="9" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="G64" s="10">
         <v>0.75</v>
@@ -3897,28 +3939,28 @@
         <v>32</v>
       </c>
       <c r="J64" s="9" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="K64" s="8"/>
     </row>
     <row r="65" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="20" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B65" s="21">
         <v>5</v>
       </c>
       <c r="C65" s="20" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="G65" s="10">
         <v>0.75</v>
@@ -3930,61 +3972,61 @@
         <v>32</v>
       </c>
       <c r="J65" s="9" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="K65" s="8"/>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="20" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="B66" s="21">
         <v>5</v>
       </c>
       <c r="C66" s="20" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="F66" s="9" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G66" s="10">
         <v>0.75</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="I66" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J66" s="9" t="s">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="K66" s="8"/>
     </row>
     <row r="67" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="20" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B67" s="21">
         <v>5</v>
       </c>
       <c r="C67" s="20" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="G67" s="10">
         <v>0.5</v>
@@ -3996,25 +4038,25 @@
         <v>32</v>
       </c>
       <c r="J67" s="9" t="s">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="K67" s="8"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="22" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B68" s="23">
         <v>6</v>
       </c>
       <c r="C68" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D68" s="7" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="F68" s="9" t="s">
         <v>112</v>
@@ -4029,28 +4071,28 @@
         <v>32</v>
       </c>
       <c r="J68" s="9" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="K68" s="8"/>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="22" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="B69" s="23">
         <v>6</v>
       </c>
       <c r="C69" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="F69" s="9" t="s">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="G69" s="10">
         <v>0.75</v>
@@ -4062,25 +4104,25 @@
         <v>32</v>
       </c>
       <c r="J69" s="9" t="s">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="K69" s="8"/>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="22" t="s">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B70" s="23">
         <v>6</v>
       </c>
       <c r="C70" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D70" s="7" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="F70" s="9" t="s">
         <v>107</v>
@@ -4095,28 +4137,28 @@
         <v>32</v>
       </c>
       <c r="J70" s="9" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="K70" s="8"/>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="22" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="B71" s="23">
         <v>6</v>
       </c>
       <c r="C71" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="F71" s="9" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G71" s="10">
         <v>0.4</v>
@@ -4128,28 +4170,28 @@
         <v>32</v>
       </c>
       <c r="J71" s="9" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="K71" s="8"/>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="22" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="B72" s="23">
         <v>6</v>
       </c>
       <c r="C72" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="F72" s="9" t="s">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="G72" s="10">
         <v>0.4</v>
@@ -4161,25 +4203,25 @@
         <v>32</v>
       </c>
       <c r="J72" s="9" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="K72" s="8"/>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="22" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B73" s="23">
         <v>6</v>
       </c>
       <c r="C73" s="22" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>112</v>
@@ -4188,34 +4230,34 @@
         <v>0.6</v>
       </c>
       <c r="H73" s="11" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="I73" s="9" t="s">
         <v>32</v>
       </c>
       <c r="J73" s="9" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="K73" s="8"/>
     </row>
     <row r="74" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="22" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B74" s="23">
         <v>6</v>
       </c>
       <c r="C74" s="22" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D74" s="7" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="F74" s="9" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G74" s="10">
         <v>0.75</v>
@@ -4227,28 +4269,28 @@
         <v>32</v>
       </c>
       <c r="J74" s="9" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="K74" s="8"/>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="22" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="B75" s="23">
         <v>6</v>
       </c>
       <c r="C75" s="22" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="F75" s="9" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="G75" s="10">
         <v>0.5</v>
@@ -4260,28 +4302,28 @@
         <v>32</v>
       </c>
       <c r="J75" s="9" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="K75" s="8"/>
     </row>
     <row r="76" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="22" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B76" s="23">
         <v>6</v>
       </c>
       <c r="C76" s="22" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="F76" s="9" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="G76" s="10">
         <v>0.75</v>
@@ -4293,28 +4335,28 @@
         <v>32</v>
       </c>
       <c r="J76" s="9" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="K76" s="8"/>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="22" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B77" s="23">
         <v>6</v>
       </c>
       <c r="C77" s="22" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="F77" s="9" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="G77" s="10">
         <v>1</v>
@@ -4330,7 +4372,7 @@
     </row>
     <row r="78" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="22" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B78" s="23">
         <v>0</v>
@@ -4339,10 +4381,10 @@
         <v>54</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>48</v>
@@ -4357,15 +4399,15 @@
         <v>38</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="K78" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="79" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="22" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B79" s="23">
         <v>0</v>
@@ -4374,10 +4416,10 @@
         <v>54</v>
       </c>
       <c r="D79" s="7" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>40</v>
@@ -4386,28 +4428,60 @@
         <v>0.5</v>
       </c>
       <c r="H79" s="11" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="I79" s="9" t="s">
         <v>38</v>
       </c>
       <c r="J79" s="9" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="K79" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="D80" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="F80" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="G80" s="25">
-        <f>SUM(G6:G79)</f>
-        <v>39.899999999999991</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A80" s="22" t="s">
+        <v>354</v>
+      </c>
+      <c r="B80" s="23">
+        <v>4</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="E80" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="F80" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="G80" s="10">
+        <v>0.5</v>
+      </c>
+      <c r="H80" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="J80" s="9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="81" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D81" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="F81" s="24" t="s">
+        <v>359</v>
+      </c>
+      <c r="G81" s="25">
+        <f>SUM(G6:G80)</f>
+        <v>40.399999999999991</v>
       </c>
     </row>
   </sheetData>
@@ -4455,12 +4529,12 @@
   <sheetData>
     <row r="1" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -4468,13 +4542,13 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>38</v>
@@ -4483,13 +4557,13 @@
         <v>9</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4500,22 +4574,22 @@
         <v>15</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="D5" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A5)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A5)</f>
         <v>11</v>
       </c>
       <c r="E5" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A5,Tasks!$I$6:$I$80,"Done")</f>
         <v>5</v>
       </c>
       <c r="F5" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A5)</f>
         <v>3.75</v>
       </c>
       <c r="G5" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A5,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A5,Tasks!$I$6:$I$80,"Done")</f>
         <v>2</v>
       </c>
       <c r="H5" s="28">
@@ -4523,7 +4597,7 @@
         <v>0.53333333333333333</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -4531,25 +4605,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="D6" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A6)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A6)</f>
         <v>11</v>
       </c>
       <c r="E6" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A6,Tasks!$I$6:$I$80,"Done")</f>
         <v>11</v>
       </c>
       <c r="F6" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A6)</f>
         <v>6</v>
       </c>
       <c r="G6" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A6,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A6,Tasks!$I$6:$I$80,"Done")</f>
         <v>6</v>
       </c>
       <c r="H6" s="28">
@@ -4557,7 +4631,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -4565,25 +4639,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="D7" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A7)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A7)</f>
         <v>10</v>
       </c>
       <c r="E7" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A7,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A7,Tasks!$I$6:$I$80,"Done")</f>
         <v>10</v>
       </c>
       <c r="F7" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A7)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A7)</f>
         <v>5.3000000000000007</v>
       </c>
       <c r="G7" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A7,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A7,Tasks!$I$6:$I$80,"Done")</f>
         <v>5.3000000000000007</v>
       </c>
       <c r="H7" s="28">
@@ -4591,7 +4665,7 @@
         <v>1</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4599,25 +4673,25 @@
         <v>3</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="D8" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A8)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A8)</f>
         <v>11</v>
       </c>
       <c r="E8" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A8,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A8,Tasks!$I$6:$I$80,"Done")</f>
         <v>11</v>
       </c>
       <c r="F8" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A8)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A8)</f>
         <v>5.7000000000000011</v>
       </c>
       <c r="G8" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A8,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A8,Tasks!$I$6:$I$80,"Done")</f>
         <v>5.7000000000000011</v>
       </c>
       <c r="H8" s="28">
@@ -4625,7 +4699,7 @@
         <v>1</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -4633,25 +4707,25 @@
         <v>4</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="D9" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A9)</f>
-        <v>11</v>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A9)</f>
+        <v>12</v>
       </c>
       <c r="E9" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A9,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A9,Tasks!$I$6:$I$80,"Done")</f>
         <v>0</v>
       </c>
       <c r="F9" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A9)</f>
-        <v>6.5500000000000007</v>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A9)</f>
+        <v>7.0500000000000007</v>
       </c>
       <c r="G9" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A9,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A9,Tasks!$I$6:$I$80,"Done")</f>
         <v>0</v>
       </c>
       <c r="H9" s="28">
@@ -4659,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4667,25 +4741,25 @@
         <v>5</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="D10" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A10)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A10)</f>
         <v>10</v>
       </c>
       <c r="E10" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A10,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A10,Tasks!$I$6:$I$80,"Done")</f>
         <v>0</v>
       </c>
       <c r="F10" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A10)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A10)</f>
         <v>6.3</v>
       </c>
       <c r="G10" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A10,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A10,Tasks!$I$6:$I$80,"Done")</f>
         <v>0</v>
       </c>
       <c r="H10" s="28">
@@ -4693,7 +4767,7 @@
         <v>0</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -4701,25 +4775,25 @@
         <v>6</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D11" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A11)</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A11)</f>
         <v>10</v>
       </c>
       <c r="E11" s="27">
-        <f>COUNTIFS(Tasks!$B$6:$B$79,$A11,Tasks!$I$6:$I$79,"Done")</f>
+        <f>COUNTIFS(Tasks!$B$6:$B$80,$A11,Tasks!$I$6:$I$80,"Done")</f>
         <v>0</v>
       </c>
       <c r="F11" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A11)</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A11)</f>
         <v>6.3</v>
       </c>
       <c r="G11" s="10">
-        <f>SUMIFS(Tasks!$G$6:$G$79,Tasks!$B$6:$B$79,$A11,Tasks!$I$6:$I$79,"Done")</f>
+        <f>SUMIFS(Tasks!$G$6:$G$80,Tasks!$B$6:$B$80,$A11,Tasks!$I$6:$I$80,"Done")</f>
         <v>0</v>
       </c>
       <c r="H11" s="28">
@@ -4727,18 +4801,18 @@
         <v>0</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="35"/>
       <c r="B12" s="35" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="C12" s="35"/>
       <c r="D12" s="36">
         <f>SUM(D5:D11)</f>
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E12" s="36">
         <f>SUM(E5:E11)</f>
@@ -4746,7 +4820,7 @@
       </c>
       <c r="F12" s="37">
         <f>SUM(F5:F11)</f>
-        <v>39.9</v>
+        <v>40.4</v>
       </c>
       <c r="G12" s="37">
         <f>SUM(G5:G11)</f>
@@ -4754,13 +4828,13 @@
       </c>
       <c r="H12" s="38">
         <f t="shared" si="0"/>
-        <v>0.47619047619047622</v>
+        <v>0.47029702970297033</v>
       </c>
       <c r="I12" s="35"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B14" s="39" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
     </row>
   </sheetData>
@@ -4779,7 +4853,7 @@
   <sheetData>
     <row r="1" spans="1:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -4788,10 +4862,10 @@
     </row>
     <row r="4" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="24" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -4800,7 +4874,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B6" s="40"/>
     </row>
@@ -4809,23 +4883,23 @@
         <v>32</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="24" t="s">
-        <v>383</v>
+        <v>213</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="24" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -4833,7 +4907,7 @@
         <v>38</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -4841,7 +4915,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -4850,7 +4924,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B13" s="40"/>
     </row>
@@ -4859,23 +4933,23 @@
         <v>18</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="24" t="s">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="24" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -4884,7 +4958,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="41" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="B18" s="40"/>
     </row>
@@ -4893,7 +4967,7 @@
         <v>8</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -4901,7 +4975,7 @@
         <v>9</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -4909,7 +4983,7 @@
         <v>12</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -4918,10 +4992,10 @@
     </row>
     <row r="23" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="24" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="B23" s="40" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -4930,10 +5004,10 @@
     </row>
     <row r="25" spans="1:2" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="24" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
